--- a/research/traditional_assets/database/data/thailand/thailand_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_real_estate_general_diversified.xlsx
@@ -1784,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1921,22 +1921,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07986702271770341</v>
+        <v>0.07974328867226799</v>
       </c>
       <c r="C2">
-        <v>185.9810088511689</v>
+        <v>184.9803865070073</v>
       </c>
       <c r="D2">
-        <v>185.5470088511689</v>
+        <v>186.2233865070073</v>
       </c>
       <c r="E2">
-        <v>-145.5</v>
+        <v>-143.823</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.677</v>
       </c>
       <c r="G2">
         <v>0.434</v>
@@ -1957,28 +1957,28 @@
         <v>29.9</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08435309999999999</v>
       </c>
       <c r="N2">
-        <v>29.9</v>
+        <v>29.8156469</v>
       </c>
       <c r="O2">
-        <v>5.98</v>
+        <v>5.963129380000001</v>
       </c>
       <c r="P2">
-        <v>23.92</v>
+        <v>23.85251752</v>
       </c>
       <c r="Q2">
-        <v>26.82</v>
+        <v>26.75251752</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07986702271770341</v>
+        <v>0.08014231179016969</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5312646412299744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>354.4623730485306</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07974328867226799</v>
+        <v>0.07961955462683258</v>
       </c>
       <c r="C3">
-        <v>184.9803865070073</v>
+        <v>183.9847134263427</v>
       </c>
       <c r="D3">
-        <v>186.2233865070073</v>
+        <v>186.9047134263427</v>
       </c>
       <c r="E3">
-        <v>-143.823</v>
+        <v>-142.146</v>
       </c>
       <c r="F3">
-        <v>1.677</v>
+        <v>3.354</v>
       </c>
       <c r="G3">
         <v>0.434</v>
@@ -2039,28 +2039,28 @@
         <v>29.9</v>
       </c>
       <c r="M3">
-        <v>0.08435309999999999</v>
+        <v>0.1687062</v>
       </c>
       <c r="N3">
-        <v>29.8156469</v>
+        <v>29.7312938</v>
       </c>
       <c r="O3">
-        <v>5.963129380000001</v>
+        <v>5.946258760000001</v>
       </c>
       <c r="P3">
-        <v>23.85251752</v>
+        <v>23.78503504</v>
       </c>
       <c r="Q3">
-        <v>26.75251752</v>
+        <v>26.68503504000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08014231179016969</v>
+        <v>0.08042321900697202</v>
       </c>
       <c r="T3">
-        <v>0.5312646412299744</v>
+        <v>0.5356101865347062</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>354.4623730485306</v>
+        <v>177.2311865242653</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2085,22 +2085,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07961955462683258</v>
+        <v>0.07949582058139718</v>
       </c>
       <c r="C4">
-        <v>183.9847134263427</v>
+        <v>182.9940441315802</v>
       </c>
       <c r="D4">
-        <v>186.9047134263427</v>
+        <v>187.5910441315802</v>
       </c>
       <c r="E4">
-        <v>-142.146</v>
+        <v>-140.469</v>
       </c>
       <c r="F4">
-        <v>3.354</v>
+        <v>5.031</v>
       </c>
       <c r="G4">
         <v>0.434</v>
@@ -2121,28 +2121,28 @@
         <v>29.9</v>
       </c>
       <c r="M4">
-        <v>0.1687062</v>
+        <v>0.2530593</v>
       </c>
       <c r="N4">
-        <v>29.7312938</v>
+        <v>29.6469407</v>
       </c>
       <c r="O4">
-        <v>5.946258760000001</v>
+        <v>5.92938814</v>
       </c>
       <c r="P4">
-        <v>23.78503504</v>
+        <v>23.71755256</v>
       </c>
       <c r="Q4">
-        <v>26.68503504000001</v>
+        <v>26.61755256</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08042321900697202</v>
+        <v>0.08070991812515173</v>
       </c>
       <c r="T4">
-        <v>0.5356101865347062</v>
+        <v>0.5400453307117002</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>177.2311865242653</v>
+        <v>118.1541243495102</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2167,22 +2167,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07949582058139718</v>
+        <v>0.07937208653596177</v>
       </c>
       <c r="C5">
-        <v>182.9940441315802</v>
+        <v>182.0084339489211</v>
       </c>
       <c r="D5">
-        <v>187.5910441315802</v>
+        <v>188.2824339489211</v>
       </c>
       <c r="E5">
-        <v>-140.469</v>
+        <v>-138.792</v>
       </c>
       <c r="F5">
-        <v>5.031</v>
+        <v>6.707999999999999</v>
       </c>
       <c r="G5">
         <v>0.434</v>
@@ -2203,28 +2203,28 @@
         <v>29.9</v>
       </c>
       <c r="M5">
-        <v>0.2530593</v>
+        <v>0.3374123999999999</v>
       </c>
       <c r="N5">
-        <v>29.6469407</v>
+        <v>29.5625876</v>
       </c>
       <c r="O5">
-        <v>5.92938814</v>
+        <v>5.912517520000001</v>
       </c>
       <c r="P5">
-        <v>23.71755256</v>
+        <v>23.65007008</v>
       </c>
       <c r="Q5">
-        <v>26.61755256</v>
+        <v>26.55007008</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08070991812515173</v>
+        <v>0.08100259014162685</v>
       </c>
       <c r="T5">
-        <v>0.5400453307117002</v>
+        <v>0.5445728737257153</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>118.1541243495102</v>
+        <v>88.61559326213265</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2249,22 +2249,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07937208653596177</v>
+        <v>0.07924835249052635</v>
       </c>
       <c r="C6">
-        <v>182.0084339489211</v>
+        <v>181.0279390232301</v>
       </c>
       <c r="D6">
-        <v>188.2824339489211</v>
+        <v>188.9789390232301</v>
       </c>
       <c r="E6">
-        <v>-138.792</v>
+        <v>-137.115</v>
       </c>
       <c r="F6">
-        <v>6.707999999999999</v>
+        <v>8.385</v>
       </c>
       <c r="G6">
         <v>0.434</v>
@@ -2285,28 +2285,28 @@
         <v>29.9</v>
       </c>
       <c r="M6">
-        <v>0.3374123999999999</v>
+        <v>0.4217655</v>
       </c>
       <c r="N6">
-        <v>29.5625876</v>
+        <v>29.4782345</v>
       </c>
       <c r="O6">
-        <v>5.912517520000001</v>
+        <v>5.895646900000001</v>
       </c>
       <c r="P6">
-        <v>23.65007008</v>
+        <v>23.5825876</v>
       </c>
       <c r="Q6">
-        <v>26.55007008</v>
+        <v>26.48258760000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08100259014162685</v>
+        <v>0.08130142367423827</v>
       </c>
       <c r="T6">
-        <v>0.5445728737257153</v>
+        <v>0.549195733434762</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2323,7 +2323,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>88.61559326213265</v>
+        <v>70.89247460970611</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2331,22 +2331,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07924835249052635</v>
+        <v>0.07912461844509096</v>
       </c>
       <c r="C7">
-        <v>181.0279390232301</v>
+        <v>180.0526163332332</v>
       </c>
       <c r="D7">
-        <v>188.9789390232301</v>
+        <v>189.6806163332332</v>
       </c>
       <c r="E7">
-        <v>-137.115</v>
+        <v>-135.438</v>
       </c>
       <c r="F7">
-        <v>8.385</v>
+        <v>10.062</v>
       </c>
       <c r="G7">
         <v>0.434</v>
@@ -2367,28 +2367,28 @@
         <v>29.9</v>
       </c>
       <c r="M7">
-        <v>0.4217655</v>
+        <v>0.5061186</v>
       </c>
       <c r="N7">
-        <v>29.4782345</v>
+        <v>29.3938814</v>
       </c>
       <c r="O7">
-        <v>5.895646900000001</v>
+        <v>5.87877628</v>
       </c>
       <c r="P7">
-        <v>23.5825876</v>
+        <v>23.51510512</v>
       </c>
       <c r="Q7">
-        <v>26.48258760000001</v>
+        <v>26.41510512</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08130142367423827</v>
+        <v>0.08160661536711805</v>
       </c>
       <c r="T7">
-        <v>0.549195733434762</v>
+        <v>0.5539169518610227</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2405,7 +2405,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>70.89247460970611</v>
+        <v>59.07706217475509</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07912461844509096</v>
+        <v>0.07900088439965555</v>
       </c>
       <c r="C8">
-        <v>180.0526163332332</v>
+        <v>179.0825237070571</v>
       </c>
       <c r="D8">
-        <v>189.6806163332332</v>
+        <v>190.3875237070571</v>
       </c>
       <c r="E8">
-        <v>-135.438</v>
+        <v>-133.761</v>
       </c>
       <c r="F8">
-        <v>10.062</v>
+        <v>11.739</v>
       </c>
       <c r="G8">
         <v>0.434</v>
@@ -2449,28 +2449,28 @@
         <v>29.9</v>
       </c>
       <c r="M8">
-        <v>0.5061186</v>
+        <v>0.5904716999999998</v>
       </c>
       <c r="N8">
-        <v>29.3938814</v>
+        <v>29.3095283</v>
       </c>
       <c r="O8">
-        <v>5.87877628</v>
+        <v>5.861905660000001</v>
       </c>
       <c r="P8">
-        <v>23.51510512</v>
+        <v>23.44762264</v>
       </c>
       <c r="Q8">
-        <v>26.41510512</v>
+        <v>26.34762264</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08160661536711805</v>
+        <v>0.08191837032221028</v>
       </c>
       <c r="T8">
-        <v>0.5539169518610227</v>
+        <v>0.5587397018663427</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>59.07706217475509</v>
+        <v>50.63748186407581</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2495,22 +2495,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07900088439965555</v>
+        <v>0.07887715035422016</v>
       </c>
       <c r="C9">
-        <v>179.0825237070571</v>
+        <v>178.1177198381152</v>
       </c>
       <c r="D9">
-        <v>190.3875237070571</v>
+        <v>191.0997198381152</v>
       </c>
       <c r="E9">
-        <v>-133.761</v>
+        <v>-132.084</v>
       </c>
       <c r="F9">
-        <v>11.739</v>
+        <v>13.416</v>
       </c>
       <c r="G9">
         <v>0.434</v>
@@ -2531,28 +2531,28 @@
         <v>29.9</v>
       </c>
       <c r="M9">
-        <v>0.5904717</v>
+        <v>0.6748247999999999</v>
       </c>
       <c r="N9">
-        <v>29.3095283</v>
+        <v>29.2251752</v>
       </c>
       <c r="O9">
-        <v>5.861905660000001</v>
+        <v>5.845035040000001</v>
       </c>
       <c r="P9">
-        <v>23.44762264</v>
+        <v>23.38014016</v>
       </c>
       <c r="Q9">
-        <v>26.34762264</v>
+        <v>26.28014016000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08191837032221028</v>
+        <v>0.08223690255893494</v>
       </c>
       <c r="T9">
-        <v>0.5587397018663427</v>
+        <v>0.5636672942630826</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>50.6374818640758</v>
+        <v>44.30779663106632</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2577,22 +2577,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07887715035422016</v>
+        <v>0.07875341630878474</v>
       </c>
       <c r="C10">
-        <v>178.1177198381152</v>
+        <v>177.1582643013532</v>
       </c>
       <c r="D10">
-        <v>191.0997198381152</v>
+        <v>191.8172643013532</v>
       </c>
       <c r="E10">
-        <v>-132.084</v>
+        <v>-130.407</v>
       </c>
       <c r="F10">
-        <v>13.416</v>
+        <v>15.093</v>
       </c>
       <c r="G10">
         <v>0.434</v>
@@ -2613,28 +2613,28 @@
         <v>29.9</v>
       </c>
       <c r="M10">
-        <v>0.6748247999999999</v>
+        <v>0.7591778999999999</v>
       </c>
       <c r="N10">
-        <v>29.2251752</v>
+        <v>29.1408221</v>
       </c>
       <c r="O10">
-        <v>5.845035040000001</v>
+        <v>5.82816442</v>
       </c>
       <c r="P10">
-        <v>23.38014016</v>
+        <v>23.31265768</v>
       </c>
       <c r="Q10">
-        <v>26.28014016000001</v>
+        <v>26.21265768</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08223690255893494</v>
+        <v>0.08256243550415905</v>
       </c>
       <c r="T10">
-        <v>0.5636672942630826</v>
+        <v>0.5687031853938168</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>44.30779663106632</v>
+        <v>39.3847081165034</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2659,22 +2659,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07875341630878474</v>
+        <v>0.07862968226334933</v>
       </c>
       <c r="C11">
-        <v>177.1582643013532</v>
+        <v>176.2042175698609</v>
       </c>
       <c r="D11">
-        <v>191.8172643013532</v>
+        <v>192.5402175698609</v>
       </c>
       <c r="E11">
-        <v>-130.407</v>
+        <v>-128.73</v>
       </c>
       <c r="F11">
-        <v>15.093</v>
+        <v>16.77</v>
       </c>
       <c r="G11">
         <v>0.434</v>
@@ -2695,28 +2695,28 @@
         <v>29.9</v>
       </c>
       <c r="M11">
-        <v>0.7591778999999999</v>
+        <v>0.8435309999999998</v>
       </c>
       <c r="N11">
-        <v>29.1408221</v>
+        <v>29.056469</v>
       </c>
       <c r="O11">
-        <v>5.82816442</v>
+        <v>5.811293800000001</v>
       </c>
       <c r="P11">
-        <v>23.31265768</v>
+        <v>23.2451752</v>
       </c>
       <c r="Q11">
-        <v>26.21265768</v>
+        <v>26.1451752</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08256243550415905</v>
+        <v>0.08289520251483259</v>
       </c>
       <c r="T11">
-        <v>0.5687031853938168</v>
+        <v>0.573850985216345</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>39.3847081165034</v>
+        <v>35.44623730485306</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2741,22 +2741,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07862968226334933</v>
+        <v>0.07850594821791392</v>
       </c>
       <c r="C12">
-        <v>176.2042175698609</v>
+        <v>175.2556410318624</v>
       </c>
       <c r="D12">
-        <v>192.5402175698609</v>
+        <v>193.2686410318624</v>
       </c>
       <c r="E12">
-        <v>-128.73</v>
+        <v>-127.053</v>
       </c>
       <c r="F12">
-        <v>16.77</v>
+        <v>18.447</v>
       </c>
       <c r="G12">
         <v>0.434</v>
@@ -2777,28 +2777,28 @@
         <v>29.9</v>
       </c>
       <c r="M12">
-        <v>0.8435309999999999</v>
+        <v>0.9278840999999999</v>
       </c>
       <c r="N12">
-        <v>29.056469</v>
+        <v>28.9721159</v>
       </c>
       <c r="O12">
-        <v>5.811293800000001</v>
+        <v>5.794423180000001</v>
       </c>
       <c r="P12">
-        <v>23.2451752</v>
+        <v>23.17769272</v>
       </c>
       <c r="Q12">
-        <v>26.1451752</v>
+        <v>26.07769272000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08289520251483259</v>
+        <v>0.08323544743585834</v>
       </c>
       <c r="T12">
-        <v>0.5738509852163451</v>
+        <v>0.5791144659337617</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>35.44623730485306</v>
+        <v>32.22385209532096</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2823,22 +2823,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07850594821791392</v>
+        <v>0.07838221417247851</v>
       </c>
       <c r="C13">
-        <v>175.2556410318624</v>
+        <v>174.3125970080918</v>
       </c>
       <c r="D13">
-        <v>193.2686410318624</v>
+        <v>194.0025970080918</v>
       </c>
       <c r="E13">
-        <v>-127.053</v>
+        <v>-125.376</v>
       </c>
       <c r="F13">
-        <v>18.447</v>
+        <v>20.124</v>
       </c>
       <c r="G13">
         <v>0.434</v>
@@ -2859,28 +2859,28 @@
         <v>29.9</v>
       </c>
       <c r="M13">
-        <v>0.9278840999999999</v>
+        <v>1.0122372</v>
       </c>
       <c r="N13">
-        <v>28.9721159</v>
+        <v>28.8877628</v>
       </c>
       <c r="O13">
-        <v>5.794423180000001</v>
+        <v>5.77755256</v>
       </c>
       <c r="P13">
-        <v>23.17769272</v>
+        <v>23.11021024</v>
       </c>
       <c r="Q13">
-        <v>26.07769272000001</v>
+        <v>26.01021024</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08323544743585834</v>
+        <v>0.08358342519599832</v>
       </c>
       <c r="T13">
-        <v>0.5791144659337617</v>
+        <v>0.5844975712129378</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>32.22385209532096</v>
+        <v>29.53853108737755</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2905,22 +2905,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07838221417247851</v>
+        <v>0.0782584801270431</v>
       </c>
       <c r="C14">
-        <v>174.3125970080918</v>
+        <v>173.3751487695677</v>
       </c>
       <c r="D14">
-        <v>194.0025970080918</v>
+        <v>194.7421487695677</v>
       </c>
       <c r="E14">
-        <v>-125.376</v>
+        <v>-123.699</v>
       </c>
       <c r="F14">
-        <v>20.124</v>
+        <v>21.801</v>
       </c>
       <c r="G14">
         <v>0.434</v>
@@ -2941,28 +2941,28 @@
         <v>29.9</v>
       </c>
       <c r="M14">
-        <v>1.0122372</v>
+        <v>1.0965903</v>
       </c>
       <c r="N14">
-        <v>28.8877628</v>
+        <v>28.8034097</v>
       </c>
       <c r="O14">
-        <v>5.77755256</v>
+        <v>5.760681940000001</v>
       </c>
       <c r="P14">
-        <v>23.11021024</v>
+        <v>23.04272776</v>
       </c>
       <c r="Q14">
-        <v>26.01021024</v>
+        <v>25.94272776</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08358342519599832</v>
+        <v>0.08393940244487713</v>
       </c>
       <c r="T14">
-        <v>0.5844975712129378</v>
+        <v>0.5900044260387616</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2979,7 +2979,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>29.53853108737755</v>
+        <v>27.26633638834851</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2987,22 +2987,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0782584801270431</v>
+        <v>0.07813474608160771</v>
       </c>
       <c r="C15">
-        <v>173.3751487695677</v>
+        <v>172.4433605557751</v>
       </c>
       <c r="D15">
-        <v>194.7421487695677</v>
+        <v>195.4873605557752</v>
       </c>
       <c r="E15">
-        <v>-123.699</v>
+        <v>-122.022</v>
       </c>
       <c r="F15">
-        <v>21.801</v>
+        <v>23.478</v>
       </c>
       <c r="G15">
         <v>0.434</v>
@@ -3023,28 +3023,28 @@
         <v>29.9</v>
       </c>
       <c r="M15">
-        <v>1.0965903</v>
+        <v>1.1809434</v>
       </c>
       <c r="N15">
-        <v>28.8034097</v>
+        <v>28.7190566</v>
       </c>
       <c r="O15">
-        <v>5.760681940000001</v>
+        <v>5.743811320000001</v>
       </c>
       <c r="P15">
-        <v>23.04272776</v>
+        <v>22.97524528</v>
       </c>
       <c r="Q15">
-        <v>25.94272776</v>
+        <v>25.87524528000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08393940244487713</v>
+        <v>0.08430365823442756</v>
       </c>
       <c r="T15">
-        <v>0.5900044260387616</v>
+        <v>0.5956393472558836</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>27.26633638834851</v>
+        <v>25.31874093203789</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07813474608160771</v>
+        <v>0.07801101203617231</v>
       </c>
       <c r="C16">
-        <v>172.4433605557751</v>
+        <v>171.517297593267</v>
       </c>
       <c r="D16">
-        <v>195.4873605557752</v>
+        <v>196.238297593267</v>
       </c>
       <c r="E16">
-        <v>-122.022</v>
+        <v>-120.345</v>
       </c>
       <c r="F16">
-        <v>23.478</v>
+        <v>25.155</v>
       </c>
       <c r="G16">
         <v>0.434</v>
@@ -3105,28 +3105,28 @@
         <v>29.9</v>
       </c>
       <c r="M16">
-        <v>1.1809434</v>
+        <v>1.2652965</v>
       </c>
       <c r="N16">
-        <v>28.7190566</v>
+        <v>28.6347035</v>
       </c>
       <c r="O16">
-        <v>5.743811320000001</v>
+        <v>5.7269407</v>
       </c>
       <c r="P16">
-        <v>22.97524528</v>
+        <v>22.9077628</v>
       </c>
       <c r="Q16">
-        <v>25.87524528000001</v>
+        <v>25.8077628</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08430365823442756</v>
+        <v>0.084676484748438</v>
       </c>
       <c r="T16">
-        <v>0.5956393472558836</v>
+        <v>0.601406854854585</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>25.31874093203789</v>
+        <v>23.63082486990204</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3151,22 +3151,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07801101203617231</v>
+        <v>0.07788727799073689</v>
       </c>
       <c r="C17">
-        <v>171.517297593267</v>
+        <v>170.5970261146948</v>
       </c>
       <c r="D17">
-        <v>196.238297593267</v>
+        <v>196.9950261146948</v>
       </c>
       <c r="E17">
-        <v>-120.345</v>
+        <v>-118.668</v>
       </c>
       <c r="F17">
-        <v>25.155</v>
+        <v>26.832</v>
       </c>
       <c r="G17">
         <v>0.434</v>
@@ -3187,28 +3187,28 @@
         <v>29.9</v>
       </c>
       <c r="M17">
-        <v>1.2652965</v>
+        <v>1.3496496</v>
       </c>
       <c r="N17">
-        <v>28.6347035</v>
+        <v>28.5503504</v>
       </c>
       <c r="O17">
-        <v>5.7269407</v>
+        <v>5.710070080000001</v>
       </c>
       <c r="P17">
-        <v>22.9077628</v>
+        <v>22.84028032</v>
       </c>
       <c r="Q17">
-        <v>25.8077628</v>
+        <v>25.74028032</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.084676484748438</v>
+        <v>0.08505818808421059</v>
       </c>
       <c r="T17">
-        <v>0.601406854854585</v>
+        <v>0.6073116840627792</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>23.63082486990204</v>
+        <v>22.15389831553316</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3233,22 +3233,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07788727799073689</v>
+        <v>0.07776354394530148</v>
       </c>
       <c r="C18">
-        <v>170.5970261146948</v>
+        <v>169.6826133782829</v>
       </c>
       <c r="D18">
-        <v>196.9950261146948</v>
+        <v>197.7576133782829</v>
       </c>
       <c r="E18">
-        <v>-118.668</v>
+        <v>-116.991</v>
       </c>
       <c r="F18">
-        <v>26.832</v>
+        <v>28.509</v>
       </c>
       <c r="G18">
         <v>0.434</v>
@@ -3269,28 +3269,28 @@
         <v>29.9</v>
       </c>
       <c r="M18">
-        <v>1.3496496</v>
+        <v>1.4340027</v>
       </c>
       <c r="N18">
-        <v>28.5503504</v>
+        <v>28.4659973</v>
       </c>
       <c r="O18">
-        <v>5.710070080000001</v>
+        <v>5.693199460000001</v>
       </c>
       <c r="P18">
-        <v>22.84028032</v>
+        <v>22.77279784</v>
       </c>
       <c r="Q18">
-        <v>25.74028032</v>
+        <v>25.67279784</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08505818808421059</v>
+        <v>0.08544908909072468</v>
       </c>
       <c r="T18">
-        <v>0.6073116840627792</v>
+        <v>0.6133587983121348</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>22.15389831553316</v>
+        <v>20.85072782638415</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3315,22 +3315,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07776354394530148</v>
+        <v>0.07763980989986607</v>
       </c>
       <c r="C19">
-        <v>169.6826133782829</v>
+        <v>168.7741276877558</v>
       </c>
       <c r="D19">
-        <v>197.7576133782829</v>
+        <v>198.5261276877558</v>
       </c>
       <c r="E19">
-        <v>-116.991</v>
+        <v>-115.314</v>
       </c>
       <c r="F19">
-        <v>28.509</v>
+        <v>30.186</v>
       </c>
       <c r="G19">
         <v>0.434</v>
@@ -3351,28 +3351,28 @@
         <v>29.9</v>
       </c>
       <c r="M19">
-        <v>1.4340027</v>
+        <v>1.5183558</v>
       </c>
       <c r="N19">
-        <v>28.4659973</v>
+        <v>28.3816442</v>
       </c>
       <c r="O19">
-        <v>5.693199460000001</v>
+        <v>5.676328840000001</v>
       </c>
       <c r="P19">
-        <v>22.77279784</v>
+        <v>22.70531536</v>
       </c>
       <c r="Q19">
-        <v>25.67279784</v>
+        <v>25.60531536000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08544908909072468</v>
+        <v>0.08584952426812936</v>
       </c>
       <c r="T19">
-        <v>0.6133587983121348</v>
+        <v>0.6195534031529382</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.85072782638415</v>
+        <v>19.6923540582517</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3397,22 +3397,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07763980989986609</v>
+        <v>0.07751607585443068</v>
       </c>
       <c r="C20">
-        <v>168.7741276877557</v>
+        <v>167.8716384127325</v>
       </c>
       <c r="D20">
-        <v>198.5261276877557</v>
+        <v>199.3006384127325</v>
       </c>
       <c r="E20">
-        <v>-115.314</v>
+        <v>-113.637</v>
       </c>
       <c r="F20">
-        <v>30.186</v>
+        <v>31.863</v>
       </c>
       <c r="G20">
         <v>0.434</v>
@@ -3433,28 +3433,28 @@
         <v>29.9</v>
       </c>
       <c r="M20">
-        <v>1.5183558</v>
+        <v>1.6027089</v>
       </c>
       <c r="N20">
-        <v>28.3816442</v>
+        <v>28.2972911</v>
       </c>
       <c r="O20">
-        <v>5.676328840000001</v>
+        <v>5.659458220000001</v>
       </c>
       <c r="P20">
-        <v>22.70531536</v>
+        <v>22.63783288</v>
       </c>
       <c r="Q20">
-        <v>25.60531536000001</v>
+        <v>25.53783288</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08584952426812936</v>
+        <v>0.08625984673386503</v>
       </c>
       <c r="T20">
-        <v>0.6195534031529381</v>
+        <v>0.6259009611996872</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3471,7 +3471,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>19.6923540582517</v>
+        <v>18.65591437097529</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3479,22 +3479,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07751607585443068</v>
+        <v>0.07739234180899528</v>
       </c>
       <c r="C21">
-        <v>167.8716384127325</v>
+        <v>166.9752160095995</v>
       </c>
       <c r="D21">
-        <v>199.3006384127325</v>
+        <v>200.0812160095995</v>
       </c>
       <c r="E21">
-        <v>-113.637</v>
+        <v>-111.96</v>
       </c>
       <c r="F21">
-        <v>31.863</v>
+        <v>33.54</v>
       </c>
       <c r="G21">
         <v>0.434</v>
@@ -3515,28 +3515,28 @@
         <v>29.9</v>
       </c>
       <c r="M21">
-        <v>1.6027089</v>
+        <v>1.687062</v>
       </c>
       <c r="N21">
-        <v>28.2972911</v>
+        <v>28.212938</v>
       </c>
       <c r="O21">
-        <v>5.659458220000001</v>
+        <v>5.642587600000001</v>
       </c>
       <c r="P21">
-        <v>22.63783288</v>
+        <v>22.5703504</v>
       </c>
       <c r="Q21">
-        <v>25.53783288</v>
+        <v>25.4703504</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08625984673386503</v>
+        <v>0.08668042726124409</v>
       </c>
       <c r="T21">
-        <v>0.6259009611996872</v>
+        <v>0.6324072081976048</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>18.65591437097529</v>
+        <v>17.72311865242653</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3561,22 +3561,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07739234180899528</v>
+        <v>0.07726860776355986</v>
       </c>
       <c r="C22">
-        <v>166.9752160095995</v>
+        <v>166.0849320428767</v>
       </c>
       <c r="D22">
-        <v>200.0812160095995</v>
+        <v>200.8679320428767</v>
       </c>
       <c r="E22">
-        <v>-111.96</v>
+        <v>-110.283</v>
       </c>
       <c r="F22">
-        <v>33.54</v>
+        <v>35.217</v>
       </c>
       <c r="G22">
         <v>0.434</v>
@@ -3597,28 +3597,28 @@
         <v>29.9</v>
       </c>
       <c r="M22">
-        <v>1.687062</v>
+        <v>1.7714151</v>
       </c>
       <c r="N22">
-        <v>28.212938</v>
+        <v>28.1285849</v>
       </c>
       <c r="O22">
-        <v>5.642587600000001</v>
+        <v>5.625716980000001</v>
       </c>
       <c r="P22">
-        <v>22.5703504</v>
+        <v>22.50286792</v>
       </c>
       <c r="Q22">
-        <v>25.4703504</v>
+        <v>25.40286792000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08668042726124409</v>
+        <v>0.08711165539691121</v>
       </c>
       <c r="T22">
-        <v>0.6324072081976048</v>
+        <v>0.639078170309394</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3635,7 +3635,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.72311865242653</v>
+        <v>16.8791606213586</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3643,22 +3643,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07726860776355986</v>
+        <v>0.07714487371812445</v>
       </c>
       <c r="C23">
-        <v>166.0849320428767</v>
+        <v>165.2008592070892</v>
       </c>
       <c r="D23">
-        <v>200.8679320428767</v>
+        <v>201.6608592070892</v>
       </c>
       <c r="E23">
-        <v>-110.283</v>
+        <v>-108.606</v>
       </c>
       <c r="F23">
-        <v>35.217</v>
+        <v>36.894</v>
       </c>
       <c r="G23">
         <v>0.434</v>
@@ -3679,28 +3679,28 @@
         <v>29.9</v>
       </c>
       <c r="M23">
-        <v>1.7714151</v>
+        <v>1.8557682</v>
       </c>
       <c r="N23">
-        <v>28.1285849</v>
+        <v>28.0442318</v>
       </c>
       <c r="O23">
-        <v>5.625716980000001</v>
+        <v>5.608846360000001</v>
       </c>
       <c r="P23">
-        <v>22.50286792</v>
+        <v>22.43538544</v>
       </c>
       <c r="Q23">
-        <v>25.40286792000001</v>
+        <v>25.33538544</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08711165539691121</v>
+        <v>0.08755394066426211</v>
       </c>
       <c r="T23">
-        <v>0.639078170309394</v>
+        <v>0.6459201827317417</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3717,7 +3717,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.8791606213586</v>
+        <v>16.11192604766048</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3725,22 +3725,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07714487371812445</v>
+        <v>0.07702113967268906</v>
       </c>
       <c r="C24">
-        <v>165.2008592070892</v>
+        <v>164.323071349159</v>
       </c>
       <c r="D24">
-        <v>201.6608592070892</v>
+        <v>202.460071349159</v>
       </c>
       <c r="E24">
-        <v>-108.606</v>
+        <v>-106.929</v>
       </c>
       <c r="F24">
-        <v>36.894</v>
+        <v>38.571</v>
       </c>
       <c r="G24">
         <v>0.434</v>
@@ -3761,28 +3761,28 @@
         <v>29.9</v>
       </c>
       <c r="M24">
-        <v>1.8557682</v>
+        <v>1.9401213</v>
       </c>
       <c r="N24">
-        <v>28.0442318</v>
+        <v>27.9598787</v>
       </c>
       <c r="O24">
-        <v>5.608846360000001</v>
+        <v>5.591975740000001</v>
       </c>
       <c r="P24">
-        <v>22.43538544</v>
+        <v>22.36790296</v>
       </c>
       <c r="Q24">
-        <v>25.33538544</v>
+        <v>25.26790296</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08755394066426211</v>
+        <v>0.08800771386063513</v>
       </c>
       <c r="T24">
-        <v>0.6459201827317417</v>
+        <v>0.6529399097624622</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>16.11192604766048</v>
+        <v>15.41140752384916</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3807,22 +3807,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07702113967268906</v>
+        <v>0.07689740562725364</v>
       </c>
       <c r="C25">
-        <v>164.323071349159</v>
+        <v>163.4516434913322</v>
       </c>
       <c r="D25">
-        <v>202.460071349159</v>
+        <v>203.2656434913322</v>
       </c>
       <c r="E25">
-        <v>-106.929</v>
+        <v>-105.252</v>
       </c>
       <c r="F25">
-        <v>38.571</v>
+        <v>40.248</v>
       </c>
       <c r="G25">
         <v>0.434</v>
@@ -3843,28 +3843,28 @@
         <v>29.9</v>
       </c>
       <c r="M25">
-        <v>1.9401213</v>
+        <v>2.0244744</v>
       </c>
       <c r="N25">
-        <v>27.9598787</v>
+        <v>27.8755256</v>
       </c>
       <c r="O25">
-        <v>5.591975740000001</v>
+        <v>5.575105120000001</v>
       </c>
       <c r="P25">
-        <v>22.36790296</v>
+        <v>22.30042048</v>
       </c>
       <c r="Q25">
-        <v>25.26790296</v>
+        <v>25.20042048000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08800771386063513</v>
+        <v>0.08847342845691268</v>
       </c>
       <c r="T25">
-        <v>0.6529399097624622</v>
+        <v>0.6601443664518858</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>15.41140752384916</v>
+        <v>14.76926554368877</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3889,22 +3889,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07689740562725363</v>
+        <v>0.07677367158181823</v>
       </c>
       <c r="C26">
-        <v>163.4516434913323</v>
+        <v>162.5866518546538</v>
       </c>
       <c r="D26">
-        <v>203.2656434913323</v>
+        <v>204.0776518546538</v>
       </c>
       <c r="E26">
-        <v>-105.252</v>
+        <v>-103.575</v>
       </c>
       <c r="F26">
-        <v>40.248</v>
+        <v>41.925</v>
       </c>
       <c r="G26">
         <v>0.434</v>
@@ -3925,28 +3925,28 @@
         <v>29.9</v>
       </c>
       <c r="M26">
-        <v>2.0244744</v>
+        <v>2.1088275</v>
       </c>
       <c r="N26">
-        <v>27.8755256</v>
+        <v>27.7911725</v>
       </c>
       <c r="O26">
-        <v>5.575105120000001</v>
+        <v>5.558234500000001</v>
       </c>
       <c r="P26">
-        <v>22.30042048</v>
+        <v>22.232938</v>
       </c>
       <c r="Q26">
-        <v>25.20042048000001</v>
+        <v>25.132938</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08847342845691267</v>
+        <v>0.08895156210909097</v>
       </c>
       <c r="T26">
-        <v>0.6601443664518857</v>
+        <v>0.6675409419863606</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.76926554368877</v>
+        <v>14.17849492194122</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3971,22 +3971,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07677367158181823</v>
+        <v>0.07664993753638281</v>
       </c>
       <c r="C27">
-        <v>162.5866518546538</v>
+        <v>161.7281738830098</v>
       </c>
       <c r="D27">
-        <v>204.0776518546538</v>
+        <v>204.8961738830098</v>
       </c>
       <c r="E27">
-        <v>-103.575</v>
+        <v>-101.898</v>
       </c>
       <c r="F27">
-        <v>41.925</v>
+        <v>43.602</v>
       </c>
       <c r="G27">
         <v>0.434</v>
@@ -4007,28 +4007,28 @@
         <v>29.9</v>
       </c>
       <c r="M27">
-        <v>2.1088275</v>
+        <v>2.1931806</v>
       </c>
       <c r="N27">
-        <v>27.7911725</v>
+        <v>27.7068194</v>
       </c>
       <c r="O27">
-        <v>5.558234500000001</v>
+        <v>5.54136388</v>
       </c>
       <c r="P27">
-        <v>22.232938</v>
+        <v>22.16545552</v>
       </c>
       <c r="Q27">
-        <v>25.132938</v>
+        <v>25.06545552</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08895156210909097</v>
+        <v>0.08944261829240921</v>
       </c>
       <c r="T27">
-        <v>0.6675409419863606</v>
+        <v>0.6751374249677132</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>14.17849492194122</v>
+        <v>13.63316819417425</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4053,22 +4053,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07664993753638281</v>
+        <v>0.07652620349094744</v>
       </c>
       <c r="C28">
-        <v>161.7281738830098</v>
+        <v>160.8762882677481</v>
       </c>
       <c r="D28">
-        <v>204.8961738830098</v>
+        <v>205.7212882677481</v>
       </c>
       <c r="E28">
-        <v>-101.898</v>
+        <v>-100.221</v>
       </c>
       <c r="F28">
-        <v>43.602</v>
+        <v>45.279</v>
       </c>
       <c r="G28">
         <v>0.434</v>
@@ -4089,28 +4089,28 @@
         <v>29.9</v>
       </c>
       <c r="M28">
-        <v>2.1931806</v>
+        <v>2.2775337</v>
       </c>
       <c r="N28">
-        <v>27.7068194</v>
+        <v>27.6224663</v>
       </c>
       <c r="O28">
-        <v>5.54136388</v>
+        <v>5.524493260000001</v>
       </c>
       <c r="P28">
-        <v>22.16545552</v>
+        <v>22.09797304</v>
       </c>
       <c r="Q28">
-        <v>25.06545552</v>
+        <v>24.99797304000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08944261829240921</v>
+        <v>0.08994712806979099</v>
       </c>
       <c r="T28">
-        <v>0.6751374249677132</v>
+        <v>0.6829420307704729</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>13.63316819417425</v>
+        <v>13.12823603883447</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07652620349094744</v>
+        <v>0.07673846944551201</v>
       </c>
       <c r="C29">
-        <v>160.8762882677481</v>
+        <v>157.7878536877242</v>
       </c>
       <c r="D29">
-        <v>205.7212882677481</v>
+        <v>204.3098536877242</v>
       </c>
       <c r="E29">
-        <v>-100.221</v>
+        <v>-98.544</v>
       </c>
       <c r="F29">
-        <v>45.279</v>
+        <v>46.956</v>
       </c>
       <c r="G29">
         <v>0.434</v>
@@ -4171,45 +4171,45 @@
         <v>29.9</v>
       </c>
       <c r="M29">
-        <v>2.2775337</v>
+        <v>2.4323208</v>
       </c>
       <c r="N29">
-        <v>27.6224663</v>
+        <v>27.4676792</v>
       </c>
       <c r="O29">
-        <v>5.524493260000001</v>
+        <v>5.493535840000001</v>
       </c>
       <c r="P29">
-        <v>22.09797304</v>
+        <v>21.97414336</v>
       </c>
       <c r="Q29">
-        <v>24.99797304000001</v>
+        <v>24.87414336000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08994712806979099</v>
+        <v>0.09046565200765556</v>
       </c>
       <c r="T29">
-        <v>0.6829420307704729</v>
+        <v>0.6909634311788645</v>
       </c>
       <c r="U29">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y29">
-        <v>13.12823603883447</v>
+        <v>12.29278637916512</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4217,22 +4217,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07673846944551201</v>
+        <v>0.0766267354000766</v>
       </c>
       <c r="C30">
-        <v>157.7878536877242</v>
+        <v>156.8513916064682</v>
       </c>
       <c r="D30">
-        <v>204.3098536877242</v>
+        <v>205.0503916064683</v>
       </c>
       <c r="E30">
-        <v>-98.544</v>
+        <v>-96.86699999999999</v>
       </c>
       <c r="F30">
-        <v>46.956</v>
+        <v>48.633</v>
       </c>
       <c r="G30">
         <v>0.434</v>
@@ -4253,28 +4253,28 @@
         <v>29.9</v>
       </c>
       <c r="M30">
-        <v>2.4323208</v>
+        <v>2.5191894</v>
       </c>
       <c r="N30">
-        <v>27.4676792</v>
+        <v>27.3808106</v>
       </c>
       <c r="O30">
-        <v>5.493535840000001</v>
+        <v>5.476162120000001</v>
       </c>
       <c r="P30">
-        <v>21.97414336</v>
+        <v>21.90464848</v>
       </c>
       <c r="Q30">
-        <v>24.87414336000001</v>
+        <v>24.80464848</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09046565200765556</v>
+        <v>0.09099878225362902</v>
       </c>
       <c r="T30">
-        <v>0.6909634311788645</v>
+        <v>0.6992107865283378</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>12.29278637916512</v>
+        <v>11.86889719367666</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4299,22 +4299,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0766267354000766</v>
+        <v>0.0765150013546412</v>
       </c>
       <c r="C31">
-        <v>156.8513916064683</v>
+        <v>155.9203173353252</v>
       </c>
       <c r="D31">
-        <v>205.0503916064683</v>
+        <v>205.7963173353252</v>
       </c>
       <c r="E31">
-        <v>-96.867</v>
+        <v>-95.19</v>
       </c>
       <c r="F31">
-        <v>48.633</v>
+        <v>50.31</v>
       </c>
       <c r="G31">
         <v>0.434</v>
@@ -4335,28 +4335,28 @@
         <v>29.9</v>
       </c>
       <c r="M31">
-        <v>2.5191894</v>
+        <v>2.606058</v>
       </c>
       <c r="N31">
-        <v>27.3808106</v>
+        <v>27.293942</v>
       </c>
       <c r="O31">
-        <v>5.476162120000001</v>
+        <v>5.4587884</v>
       </c>
       <c r="P31">
-        <v>21.90464848</v>
+        <v>21.8351536</v>
       </c>
       <c r="Q31">
-        <v>24.80464848</v>
+        <v>24.7351536</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09099878225362902</v>
+        <v>0.09154714479234458</v>
       </c>
       <c r="T31">
-        <v>0.6992107865283378</v>
+        <v>0.7076937806020817</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.86889719367667</v>
+        <v>11.47326728722078</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4381,22 +4381,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0765150013546412</v>
+        <v>0.0764032673092058</v>
       </c>
       <c r="C32">
-        <v>155.9203173353252</v>
+        <v>154.9946898877803</v>
       </c>
       <c r="D32">
-        <v>205.7963173353252</v>
+        <v>206.5476898877803</v>
       </c>
       <c r="E32">
-        <v>-95.19</v>
+        <v>-93.51300000000001</v>
       </c>
       <c r="F32">
-        <v>50.31</v>
+        <v>51.98699999999999</v>
       </c>
       <c r="G32">
         <v>0.434</v>
@@ -4417,28 +4417,28 @@
         <v>29.9</v>
       </c>
       <c r="M32">
-        <v>2.606058</v>
+        <v>2.6929266</v>
       </c>
       <c r="N32">
-        <v>27.293942</v>
+        <v>27.2070734</v>
       </c>
       <c r="O32">
-        <v>5.4587884</v>
+        <v>5.441414680000001</v>
       </c>
       <c r="P32">
-        <v>21.8351536</v>
+        <v>21.76565872</v>
       </c>
       <c r="Q32">
-        <v>24.7351536</v>
+        <v>24.66565872</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09154714479234458</v>
+        <v>0.09211140189739969</v>
       </c>
       <c r="T32">
-        <v>0.7076937806020817</v>
+        <v>0.7164226585620209</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.47326728722078</v>
+        <v>11.10316189085882</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4463,22 +4463,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0764032673092058</v>
+        <v>0.07629153326377039</v>
       </c>
       <c r="C33">
-        <v>154.9946898877803</v>
+        <v>154.0745691423215</v>
       </c>
       <c r="D33">
-        <v>206.5476898877803</v>
+        <v>207.3045691423215</v>
       </c>
       <c r="E33">
-        <v>-93.51300000000001</v>
+        <v>-91.83600000000001</v>
       </c>
       <c r="F33">
-        <v>51.98699999999999</v>
+        <v>53.66399999999999</v>
       </c>
       <c r="G33">
         <v>0.434</v>
@@ -4499,28 +4499,28 @@
         <v>29.9</v>
       </c>
       <c r="M33">
-        <v>2.6929266</v>
+        <v>2.7797952</v>
       </c>
       <c r="N33">
-        <v>27.2070734</v>
+        <v>27.1202048</v>
       </c>
       <c r="O33">
-        <v>5.441414680000001</v>
+        <v>5.424040960000001</v>
       </c>
       <c r="P33">
-        <v>21.76565872</v>
+        <v>21.69616384</v>
       </c>
       <c r="Q33">
-        <v>24.66565872</v>
+        <v>24.59616384000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09211140189739969</v>
+        <v>0.09269225479966234</v>
       </c>
       <c r="T33">
-        <v>0.7164226585620209</v>
+        <v>0.7254082682266644</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.10316189085882</v>
+        <v>10.75618808176948</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4545,22 +4545,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07629153326377039</v>
+        <v>0.07617979921833497</v>
       </c>
       <c r="C34">
-        <v>154.0745691423215</v>
+        <v>153.1600158583465</v>
       </c>
       <c r="D34">
-        <v>207.3045691423215</v>
+        <v>208.0670158583465</v>
       </c>
       <c r="E34">
-        <v>-91.83600000000001</v>
+        <v>-90.15899999999999</v>
       </c>
       <c r="F34">
-        <v>53.66399999999999</v>
+        <v>55.341</v>
       </c>
       <c r="G34">
         <v>0.434</v>
@@ -4581,28 +4581,28 @@
         <v>29.9</v>
       </c>
       <c r="M34">
-        <v>2.7797952</v>
+        <v>2.8666638</v>
       </c>
       <c r="N34">
-        <v>27.1202048</v>
+        <v>27.0333362</v>
       </c>
       <c r="O34">
-        <v>5.424040960000001</v>
+        <v>5.406667240000001</v>
       </c>
       <c r="P34">
-        <v>21.69616384</v>
+        <v>21.62666896</v>
       </c>
       <c r="Q34">
-        <v>24.59616384000001</v>
+        <v>24.52666896</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09269225479966234</v>
+        <v>0.09329044659452981</v>
       </c>
       <c r="T34">
-        <v>0.7254082682266644</v>
+        <v>0.7346621050454762</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.75618808176948</v>
+        <v>10.43024298838252</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4627,22 +4627,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07617979921833497</v>
+        <v>0.07606806517289956</v>
       </c>
       <c r="C35">
-        <v>153.1600158583465</v>
+        <v>152.251091692422</v>
       </c>
       <c r="D35">
-        <v>208.0670158583465</v>
+        <v>208.835091692422</v>
       </c>
       <c r="E35">
-        <v>-90.15899999999999</v>
+        <v>-88.482</v>
       </c>
       <c r="F35">
-        <v>55.341</v>
+        <v>57.018</v>
       </c>
       <c r="G35">
         <v>0.434</v>
@@ -4663,28 +4663,28 @@
         <v>29.9</v>
       </c>
       <c r="M35">
-        <v>2.8666638</v>
+        <v>2.9535324</v>
       </c>
       <c r="N35">
-        <v>27.0333362</v>
+        <v>26.9464676</v>
       </c>
       <c r="O35">
-        <v>5.406667240000001</v>
+        <v>5.389293520000001</v>
       </c>
       <c r="P35">
-        <v>21.62666896</v>
+        <v>21.55717408</v>
       </c>
       <c r="Q35">
-        <v>24.52666896</v>
+        <v>24.45717408000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09329044659452981</v>
+        <v>0.09390676541348419</v>
       </c>
       <c r="T35">
-        <v>0.7346621050454762</v>
+        <v>0.7441963611618279</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>10.43024298838252</v>
+        <v>10.12347113578304</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4709,22 +4709,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07606806517289956</v>
+        <v>0.07595633112746415</v>
       </c>
       <c r="C36">
-        <v>152.251091692422</v>
+        <v>151.3478592149048</v>
       </c>
       <c r="D36">
-        <v>208.835091692422</v>
+        <v>209.6088592149048</v>
       </c>
       <c r="E36">
-        <v>-88.482</v>
+        <v>-86.80500000000001</v>
       </c>
       <c r="F36">
-        <v>57.018</v>
+        <v>58.695</v>
       </c>
       <c r="G36">
         <v>0.434</v>
@@ -4745,28 +4745,28 @@
         <v>29.9</v>
       </c>
       <c r="M36">
-        <v>2.9535324</v>
+        <v>3.040401</v>
       </c>
       <c r="N36">
-        <v>26.9464676</v>
+        <v>26.859599</v>
       </c>
       <c r="O36">
-        <v>5.389293520000001</v>
+        <v>5.371919800000001</v>
       </c>
       <c r="P36">
-        <v>21.55717408</v>
+        <v>21.4876792</v>
       </c>
       <c r="Q36">
-        <v>24.45717408000001</v>
+        <v>24.3876792</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09390676541348419</v>
+        <v>0.09454204788840639</v>
       </c>
       <c r="T36">
-        <v>0.7441963611618279</v>
+        <v>0.7540239790048365</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4783,7 +4783,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.12347113578304</v>
+        <v>9.834229103332094</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4791,22 +4791,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07595633112746415</v>
+        <v>0.07633419708202875</v>
       </c>
       <c r="C37">
-        <v>151.3478592149048</v>
+        <v>147.0769134347142</v>
       </c>
       <c r="D37">
-        <v>209.6088592149048</v>
+        <v>207.0149134347142</v>
       </c>
       <c r="E37">
-        <v>-86.80500000000001</v>
+        <v>-85.128</v>
       </c>
       <c r="F37">
-        <v>58.695</v>
+        <v>60.372</v>
       </c>
       <c r="G37">
         <v>0.434</v>
@@ -4827,45 +4827,45 @@
         <v>29.9</v>
       </c>
       <c r="M37">
-        <v>3.040401</v>
+        <v>3.229902</v>
       </c>
       <c r="N37">
-        <v>26.859599</v>
+        <v>26.670098</v>
       </c>
       <c r="O37">
-        <v>5.371919800000001</v>
+        <v>5.334019600000001</v>
       </c>
       <c r="P37">
-        <v>21.4876792</v>
+        <v>21.3360784</v>
       </c>
       <c r="Q37">
-        <v>24.3876792</v>
+        <v>24.2360784</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09454204788840639</v>
+        <v>0.09519718294066994</v>
       </c>
       <c r="T37">
-        <v>0.7540239790048365</v>
+        <v>0.7641587099054392</v>
       </c>
       <c r="U37">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V37">
         <v>0.2</v>
       </c>
       <c r="W37">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>9.834229103332094</v>
+        <v>9.257246814299629</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4873,22 +4873,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07633419708202875</v>
+        <v>0.07623606303659336</v>
       </c>
       <c r="C38">
-        <v>147.0769134347142</v>
+        <v>146.0673851407749</v>
       </c>
       <c r="D38">
-        <v>207.0149134347142</v>
+        <v>207.6823851407749</v>
       </c>
       <c r="E38">
-        <v>-85.12800000000001</v>
+        <v>-83.45100000000001</v>
       </c>
       <c r="F38">
-        <v>60.37199999999999</v>
+        <v>62.04899999999999</v>
       </c>
       <c r="G38">
         <v>0.434</v>
@@ -4909,28 +4909,28 @@
         <v>29.9</v>
       </c>
       <c r="M38">
-        <v>3.229902</v>
+        <v>3.319621499999999</v>
       </c>
       <c r="N38">
-        <v>26.670098</v>
+        <v>26.5803785</v>
       </c>
       <c r="O38">
-        <v>5.334019600000001</v>
+        <v>5.316075700000001</v>
       </c>
       <c r="P38">
-        <v>21.3360784</v>
+        <v>21.2643028</v>
       </c>
       <c r="Q38">
-        <v>24.2360784</v>
+        <v>24.16430280000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09519718294066992</v>
+        <v>0.09587311593110055</v>
       </c>
       <c r="T38">
-        <v>0.7641587099054391</v>
+        <v>0.7746151782949499</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>9.257246814299631</v>
+        <v>9.007050954453694</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4955,22 +4955,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07623606303659336</v>
+        <v>0.07613792899115794</v>
       </c>
       <c r="C39">
-        <v>146.0673851407749</v>
+        <v>145.062174985938</v>
       </c>
       <c r="D39">
-        <v>207.6823851407749</v>
+        <v>208.354174985938</v>
       </c>
       <c r="E39">
-        <v>-83.45100000000001</v>
+        <v>-81.774</v>
       </c>
       <c r="F39">
-        <v>62.04899999999999</v>
+        <v>63.726</v>
       </c>
       <c r="G39">
         <v>0.434</v>
@@ -4991,28 +4991,28 @@
         <v>29.9</v>
       </c>
       <c r="M39">
-        <v>3.319621499999999</v>
+        <v>3.409341</v>
       </c>
       <c r="N39">
-        <v>26.5803785</v>
+        <v>26.490659</v>
       </c>
       <c r="O39">
-        <v>5.316075700000001</v>
+        <v>5.2981318</v>
       </c>
       <c r="P39">
-        <v>21.2643028</v>
+        <v>21.1925272</v>
       </c>
       <c r="Q39">
-        <v>24.16430280000001</v>
+        <v>24.0925272</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09587311593110055</v>
+        <v>0.09657085321154507</v>
       </c>
       <c r="T39">
-        <v>0.7746151782949499</v>
+        <v>0.7854089521163802</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>9.007050954453694</v>
+        <v>8.770023297757543</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5037,22 +5037,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07613792899115794</v>
+        <v>0.07603979494572254</v>
       </c>
       <c r="C40">
-        <v>145.062174985938</v>
+        <v>144.0613250098197</v>
       </c>
       <c r="D40">
-        <v>208.354174985938</v>
+        <v>209.0303250098197</v>
       </c>
       <c r="E40">
-        <v>-81.774</v>
+        <v>-80.09700000000001</v>
       </c>
       <c r="F40">
-        <v>63.726</v>
+        <v>65.40299999999999</v>
       </c>
       <c r="G40">
         <v>0.434</v>
@@ -5073,28 +5073,28 @@
         <v>29.9</v>
       </c>
       <c r="M40">
-        <v>3.409341</v>
+        <v>3.4990605</v>
       </c>
       <c r="N40">
-        <v>26.490659</v>
+        <v>26.4009395</v>
       </c>
       <c r="O40">
-        <v>5.2981318</v>
+        <v>5.280187900000001</v>
       </c>
       <c r="P40">
-        <v>21.1925272</v>
+        <v>21.1207516</v>
       </c>
       <c r="Q40">
-        <v>24.0925272</v>
+        <v>24.0207516</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09657085321154507</v>
+        <v>0.09729146712413531</v>
       </c>
       <c r="T40">
-        <v>0.7854089521163802</v>
+        <v>0.796556620161464</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.770023297757543</v>
+        <v>8.545150905507352</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5119,22 +5119,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07603979494572254</v>
+        <v>0.07594166090028713</v>
       </c>
       <c r="C41">
-        <v>144.0613250098197</v>
+        <v>143.06487779952</v>
       </c>
       <c r="D41">
-        <v>209.0303250098197</v>
+        <v>209.71087779952</v>
       </c>
       <c r="E41">
-        <v>-80.09700000000001</v>
+        <v>-78.42</v>
       </c>
       <c r="F41">
-        <v>65.40299999999999</v>
+        <v>67.08</v>
       </c>
       <c r="G41">
         <v>0.434</v>
@@ -5155,28 +5155,28 @@
         <v>29.9</v>
       </c>
       <c r="M41">
-        <v>3.4990605</v>
+        <v>3.58878</v>
       </c>
       <c r="N41">
-        <v>26.4009395</v>
+        <v>26.31122</v>
       </c>
       <c r="O41">
-        <v>5.280187900000001</v>
+        <v>5.262244000000001</v>
       </c>
       <c r="P41">
-        <v>21.1207516</v>
+        <v>21.048976</v>
       </c>
       <c r="Q41">
-        <v>24.0207516</v>
+        <v>23.94897600000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09729146712413531</v>
+        <v>0.09803610150047855</v>
       </c>
       <c r="T41">
-        <v>0.796556620161464</v>
+        <v>0.808075877141384</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -5193,7 +5193,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.545150905507352</v>
+        <v>8.331522132869667</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07594166090028713</v>
+        <v>0.07584352685485173</v>
       </c>
       <c r="C42">
-        <v>143.06487779952</v>
+        <v>142.0728764985643</v>
       </c>
       <c r="D42">
-        <v>209.71087779952</v>
+        <v>210.3958764985643</v>
       </c>
       <c r="E42">
-        <v>-78.42</v>
+        <v>-76.74299999999999</v>
       </c>
       <c r="F42">
-        <v>67.08</v>
+        <v>68.75700000000001</v>
       </c>
       <c r="G42">
         <v>0.434</v>
@@ -5237,28 +5237,28 @@
         <v>29.9</v>
       </c>
       <c r="M42">
-        <v>3.58878</v>
+        <v>3.6784995</v>
       </c>
       <c r="N42">
-        <v>26.31122</v>
+        <v>26.2215005</v>
       </c>
       <c r="O42">
-        <v>5.262244000000001</v>
+        <v>5.2443001</v>
       </c>
       <c r="P42">
-        <v>21.048976</v>
+        <v>20.9772004</v>
       </c>
       <c r="Q42">
-        <v>23.94897600000001</v>
+        <v>23.8772004</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09803610150047855</v>
+        <v>0.09880597772008767</v>
       </c>
       <c r="T42">
-        <v>0.808075877141384</v>
+        <v>0.8199856174087589</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.331522132869667</v>
+        <v>8.128314275970407</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5283,22 +5283,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07584352685485173</v>
+        <v>0.07574539280941632</v>
       </c>
       <c r="C43">
-        <v>142.0728764985643</v>
+        <v>141.0853648160206</v>
       </c>
       <c r="D43">
-        <v>210.3958764985643</v>
+        <v>211.0853648160206</v>
       </c>
       <c r="E43">
-        <v>-76.74299999999999</v>
+        <v>-75.066</v>
       </c>
       <c r="F43">
-        <v>68.75700000000001</v>
+        <v>70.434</v>
       </c>
       <c r="G43">
         <v>0.434</v>
@@ -5319,28 +5319,28 @@
         <v>29.9</v>
       </c>
       <c r="M43">
-        <v>3.6784995</v>
+        <v>3.768219</v>
       </c>
       <c r="N43">
-        <v>26.2215005</v>
+        <v>26.131781</v>
       </c>
       <c r="O43">
-        <v>5.2443001</v>
+        <v>5.226356200000001</v>
       </c>
       <c r="P43">
-        <v>20.9772004</v>
+        <v>20.9054248</v>
       </c>
       <c r="Q43">
-        <v>23.8772004</v>
+        <v>23.8054248</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09880597772008767</v>
+        <v>0.09960240139554538</v>
       </c>
       <c r="T43">
-        <v>0.8199856174087589</v>
+        <v>0.8323060383750088</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.128314275970407</v>
+        <v>7.934782983685397</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5365,22 +5365,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07574539280941632</v>
+        <v>0.07564725876398092</v>
       </c>
       <c r="C44">
-        <v>141.0853648160206</v>
+        <v>140.1023870357965</v>
       </c>
       <c r="D44">
-        <v>211.0853648160206</v>
+        <v>211.7793870357965</v>
       </c>
       <c r="E44">
-        <v>-75.066</v>
+        <v>-73.38900000000001</v>
       </c>
       <c r="F44">
-        <v>70.434</v>
+        <v>72.11099999999999</v>
       </c>
       <c r="G44">
         <v>0.434</v>
@@ -5401,28 +5401,28 @@
         <v>29.9</v>
       </c>
       <c r="M44">
-        <v>3.768219</v>
+        <v>3.857938499999999</v>
       </c>
       <c r="N44">
-        <v>26.131781</v>
+        <v>26.0420615</v>
       </c>
       <c r="O44">
-        <v>5.226356200000001</v>
+        <v>5.208412300000001</v>
       </c>
       <c r="P44">
-        <v>20.9054248</v>
+        <v>20.8336492</v>
       </c>
       <c r="Q44">
-        <v>23.8054248</v>
+        <v>23.73364920000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09960240139554537</v>
+        <v>0.10042676976137</v>
       </c>
       <c r="T44">
-        <v>0.8323060383750086</v>
+        <v>0.8450587548137586</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.934782983685397</v>
+        <v>7.750253146855504</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5447,22 +5447,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07564725876398092</v>
+        <v>0.0758307247185455</v>
       </c>
       <c r="C45">
-        <v>140.1023870357965</v>
+        <v>137.1315685294576</v>
       </c>
       <c r="D45">
-        <v>211.7793870357965</v>
+        <v>210.4855685294576</v>
       </c>
       <c r="E45">
-        <v>-73.38900000000001</v>
+        <v>-71.712</v>
       </c>
       <c r="F45">
-        <v>72.11099999999999</v>
+        <v>73.788</v>
       </c>
       <c r="G45">
         <v>0.434</v>
@@ -5483,45 +5483,45 @@
         <v>29.9</v>
       </c>
       <c r="M45">
-        <v>3.857938499999999</v>
+        <v>4.0066884</v>
       </c>
       <c r="N45">
-        <v>26.0420615</v>
+        <v>25.8933116</v>
       </c>
       <c r="O45">
-        <v>5.208412300000001</v>
+        <v>5.178662320000001</v>
       </c>
       <c r="P45">
-        <v>20.8336492</v>
+        <v>20.71464928</v>
       </c>
       <c r="Q45">
-        <v>23.73364920000001</v>
+        <v>23.61464928000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.10042676976137</v>
+        <v>0.1012805798545455</v>
       </c>
       <c r="T45">
-        <v>0.8450587548137586</v>
+        <v>0.8582669254110351</v>
       </c>
       <c r="U45">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V45">
         <v>0.2</v>
       </c>
       <c r="W45">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y45">
-        <v>7.750253146855504</v>
+        <v>7.462521917102414</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5529,22 +5529,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0758307247185455</v>
+        <v>0.0757389906731101</v>
       </c>
       <c r="C46">
-        <v>137.1315685294576</v>
+        <v>136.0995031873356</v>
       </c>
       <c r="D46">
-        <v>210.4855685294576</v>
+        <v>211.1305031873356</v>
       </c>
       <c r="E46">
-        <v>-71.712</v>
+        <v>-70.035</v>
       </c>
       <c r="F46">
-        <v>73.788</v>
+        <v>75.465</v>
       </c>
       <c r="G46">
         <v>0.434</v>
@@ -5565,28 +5565,28 @@
         <v>29.9</v>
       </c>
       <c r="M46">
-        <v>4.0066884</v>
+        <v>4.0977495</v>
       </c>
       <c r="N46">
-        <v>25.8933116</v>
+        <v>25.8022505</v>
       </c>
       <c r="O46">
-        <v>5.178662320000001</v>
+        <v>5.160450100000001</v>
       </c>
       <c r="P46">
-        <v>20.71464928</v>
+        <v>20.6418004</v>
       </c>
       <c r="Q46">
-        <v>23.61464928000001</v>
+        <v>23.5418004</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1012805798545455</v>
+        <v>0.1021654375874729</v>
       </c>
       <c r="T46">
-        <v>0.8582669254110351</v>
+        <v>0.8719553931209399</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.462521917102414</v>
+        <v>7.29668809672236</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5611,22 +5611,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.0757389906731101</v>
+        <v>0.0756472566276747</v>
       </c>
       <c r="C47">
-        <v>136.0995031873356</v>
+        <v>135.0714021938269</v>
       </c>
       <c r="D47">
-        <v>211.1305031873356</v>
+        <v>211.7794021938269</v>
       </c>
       <c r="E47">
-        <v>-70.035</v>
+        <v>-68.358</v>
       </c>
       <c r="F47">
-        <v>75.465</v>
+        <v>77.142</v>
       </c>
       <c r="G47">
         <v>0.434</v>
@@ -5647,28 +5647,28 @@
         <v>29.9</v>
       </c>
       <c r="M47">
-        <v>4.0977495</v>
+        <v>4.1888106</v>
       </c>
       <c r="N47">
-        <v>25.8022505</v>
+        <v>25.7111894</v>
       </c>
       <c r="O47">
-        <v>5.160450100000001</v>
+        <v>5.142237880000001</v>
       </c>
       <c r="P47">
-        <v>20.6418004</v>
+        <v>20.56895152</v>
       </c>
       <c r="Q47">
-        <v>23.5418004</v>
+        <v>23.46895152</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1021654375874729</v>
+        <v>0.1030830678290272</v>
       </c>
       <c r="T47">
-        <v>0.8719553931209399</v>
+        <v>0.886150841116397</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.29668809672236</v>
+        <v>7.138064442445787</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5693,22 +5693,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0756472566276747</v>
+        <v>0.0755555225822393</v>
       </c>
       <c r="C48">
-        <v>135.0714021938269</v>
+        <v>134.0473022142999</v>
       </c>
       <c r="D48">
-        <v>211.7794021938269</v>
+        <v>212.4323022142999</v>
       </c>
       <c r="E48">
-        <v>-68.358</v>
+        <v>-66.681</v>
       </c>
       <c r="F48">
-        <v>77.142</v>
+        <v>78.819</v>
       </c>
       <c r="G48">
         <v>0.434</v>
@@ -5729,28 +5729,28 @@
         <v>29.9</v>
       </c>
       <c r="M48">
-        <v>4.1888106</v>
+        <v>4.2798717</v>
       </c>
       <c r="N48">
-        <v>25.7111894</v>
+        <v>25.6201283</v>
       </c>
       <c r="O48">
-        <v>5.142237880000001</v>
+        <v>5.124025660000001</v>
       </c>
       <c r="P48">
-        <v>20.56895152</v>
+        <v>20.49610264</v>
       </c>
       <c r="Q48">
-        <v>23.46895152</v>
+        <v>23.39610264</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1030830678290272</v>
+        <v>0.1040353256268666</v>
       </c>
       <c r="T48">
-        <v>0.886150841116397</v>
+        <v>0.9008819663947013</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>7.138064442445787</v>
+        <v>6.986190730904386</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5775,22 +5775,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0755555225822393</v>
+        <v>0.07546378853680388</v>
       </c>
       <c r="C49">
-        <v>134.0473022142999</v>
+        <v>133.0272403676682</v>
       </c>
       <c r="D49">
-        <v>212.4323022142999</v>
+        <v>213.0892403676683</v>
       </c>
       <c r="E49">
-        <v>-66.681</v>
+        <v>-65.004</v>
       </c>
       <c r="F49">
-        <v>78.819</v>
+        <v>80.496</v>
       </c>
       <c r="G49">
         <v>0.434</v>
@@ -5811,28 +5811,28 @@
         <v>29.9</v>
       </c>
       <c r="M49">
-        <v>4.2798717</v>
+        <v>4.370932799999999</v>
       </c>
       <c r="N49">
-        <v>25.6201283</v>
+        <v>25.5290672</v>
       </c>
       <c r="O49">
-        <v>5.124025660000001</v>
+        <v>5.105813440000001</v>
       </c>
       <c r="P49">
-        <v>20.49610264</v>
+        <v>20.42325376</v>
       </c>
       <c r="Q49">
-        <v>23.39610264</v>
+        <v>23.32325376</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1040353256268666</v>
+        <v>0.1050242087246228</v>
       </c>
       <c r="T49">
-        <v>0.9008819663947013</v>
+        <v>0.9161796734144788</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.986190730904386</v>
+        <v>6.840645090677214</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5857,22 +5857,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07546378853680388</v>
+        <v>0.07537205449136847</v>
       </c>
       <c r="C50">
-        <v>133.0272403676682</v>
+        <v>132.0112542334243</v>
       </c>
       <c r="D50">
-        <v>213.0892403676683</v>
+        <v>213.7502542334242</v>
       </c>
       <c r="E50">
-        <v>-65.004</v>
+        <v>-63.32700000000001</v>
       </c>
       <c r="F50">
-        <v>80.496</v>
+        <v>82.17299999999999</v>
       </c>
       <c r="G50">
         <v>0.434</v>
@@ -5893,28 +5893,28 @@
         <v>29.9</v>
       </c>
       <c r="M50">
-        <v>4.370932799999999</v>
+        <v>4.4619939</v>
       </c>
       <c r="N50">
-        <v>25.5290672</v>
+        <v>25.4380061</v>
       </c>
       <c r="O50">
-        <v>5.105813440000001</v>
+        <v>5.087601220000001</v>
       </c>
       <c r="P50">
-        <v>20.42325376</v>
+        <v>20.35040488</v>
       </c>
       <c r="Q50">
-        <v>23.32325376</v>
+        <v>23.25040488</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1050242087246228</v>
+        <v>0.1060518715517029</v>
       </c>
       <c r="T50">
-        <v>0.9161796734144788</v>
+        <v>0.9320772905134633</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.840645090677214</v>
+        <v>6.701040088826658</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07537205449136847</v>
+        <v>0.07528032044593307</v>
       </c>
       <c r="C51">
-        <v>132.0112542334243</v>
+        <v>130.9993818588054</v>
       </c>
       <c r="D51">
-        <v>213.7502542334242</v>
+        <v>214.4153818588053</v>
       </c>
       <c r="E51">
-        <v>-63.32700000000001</v>
+        <v>-61.65000000000001</v>
       </c>
       <c r="F51">
-        <v>82.17299999999999</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="G51">
         <v>0.434</v>
@@ -5975,28 +5975,28 @@
         <v>29.9</v>
       </c>
       <c r="M51">
-        <v>4.4619939</v>
+        <v>4.553055</v>
       </c>
       <c r="N51">
-        <v>25.4380061</v>
+        <v>25.346945</v>
       </c>
       <c r="O51">
-        <v>5.087601220000001</v>
+        <v>5.069389000000001</v>
       </c>
       <c r="P51">
-        <v>20.35040488</v>
+        <v>20.277556</v>
       </c>
       <c r="Q51">
-        <v>23.25040488</v>
+        <v>23.177556</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1060518715517029</v>
+        <v>0.1071206408918661</v>
       </c>
       <c r="T51">
-        <v>0.9320772905134633</v>
+        <v>0.9486108122964073</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.701040088826658</v>
+        <v>6.567019287050124</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6021,22 +6021,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07528032044593307</v>
+        <v>0.07518858640049766</v>
       </c>
       <c r="C52">
-        <v>130.9993818588054</v>
+        <v>129.9916617660945</v>
       </c>
       <c r="D52">
-        <v>214.4153818588053</v>
+        <v>215.0846617660945</v>
       </c>
       <c r="E52">
-        <v>-61.65000000000001</v>
+        <v>-59.973</v>
       </c>
       <c r="F52">
-        <v>83.84999999999999</v>
+        <v>85.527</v>
       </c>
       <c r="G52">
         <v>0.434</v>
@@ -6057,28 +6057,28 @@
         <v>29.9</v>
       </c>
       <c r="M52">
-        <v>4.553055</v>
+        <v>4.6441161</v>
       </c>
       <c r="N52">
-        <v>25.346945</v>
+        <v>25.2558839</v>
       </c>
       <c r="O52">
-        <v>5.069389000000001</v>
+        <v>5.05117678</v>
       </c>
       <c r="P52">
-        <v>20.277556</v>
+        <v>20.20470712</v>
       </c>
       <c r="Q52">
-        <v>23.177556</v>
+        <v>23.10470712</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1071206408918661</v>
+        <v>0.1082330334704034</v>
       </c>
       <c r="T52">
-        <v>0.9486108122964073</v>
+        <v>0.9658191717031449</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -6095,7 +6095,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.567019287050124</v>
+        <v>6.438254202990318</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6103,22 +6103,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07518858640049766</v>
+        <v>0.07509685235506225</v>
       </c>
       <c r="C53">
-        <v>129.9916617660945</v>
+        <v>128.9881329600572</v>
       </c>
       <c r="D53">
-        <v>215.0846617660945</v>
+        <v>215.7581329600572</v>
       </c>
       <c r="E53">
-        <v>-59.973</v>
+        <v>-58.29600000000001</v>
       </c>
       <c r="F53">
-        <v>85.527</v>
+        <v>87.20399999999999</v>
       </c>
       <c r="G53">
         <v>0.434</v>
@@ -6139,28 +6139,28 @@
         <v>29.9</v>
       </c>
       <c r="M53">
-        <v>4.6441161</v>
+        <v>4.7351772</v>
       </c>
       <c r="N53">
-        <v>25.2558839</v>
+        <v>25.1648228</v>
       </c>
       <c r="O53">
-        <v>5.05117678</v>
+        <v>5.032964560000001</v>
       </c>
       <c r="P53">
-        <v>20.20470712</v>
+        <v>20.13185824</v>
       </c>
       <c r="Q53">
-        <v>23.10470712</v>
+        <v>23.03185824000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1082330334704034</v>
+        <v>0.109391775739713</v>
       </c>
       <c r="T53">
-        <v>0.9658191717031449</v>
+        <v>0.983744546085163</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.438254202990318</v>
+        <v>6.314441622163582</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6185,22 +6185,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07509685235506225</v>
+        <v>0.07500511830962685</v>
       </c>
       <c r="C54">
-        <v>128.9881329600572</v>
+        <v>127.9888349355185</v>
       </c>
       <c r="D54">
-        <v>215.7581329600572</v>
+        <v>216.4358349355185</v>
       </c>
       <c r="E54">
-        <v>-58.29600000000001</v>
+        <v>-56.619</v>
       </c>
       <c r="F54">
-        <v>87.20399999999999</v>
+        <v>88.881</v>
       </c>
       <c r="G54">
         <v>0.434</v>
@@ -6221,28 +6221,28 @@
         <v>29.9</v>
       </c>
       <c r="M54">
-        <v>4.7351772</v>
+        <v>4.8262383</v>
       </c>
       <c r="N54">
-        <v>25.1648228</v>
+        <v>25.0737617</v>
       </c>
       <c r="O54">
-        <v>5.032964560000001</v>
+        <v>5.014752340000001</v>
       </c>
       <c r="P54">
-        <v>20.13185824</v>
+        <v>20.05900936</v>
       </c>
       <c r="Q54">
-        <v>23.03185824000001</v>
+        <v>22.95900936</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.109391775739713</v>
+        <v>0.1105998261906954</v>
       </c>
       <c r="T54">
-        <v>0.983744546085163</v>
+        <v>1.002432702355778</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -6259,7 +6259,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.314441622163582</v>
+        <v>6.19530121419823</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07500511830962685</v>
+        <v>0.07534538426419143</v>
       </c>
       <c r="C55">
-        <v>127.9888349355185</v>
+        <v>123.8192037577417</v>
       </c>
       <c r="D55">
-        <v>216.4358349355185</v>
+        <v>213.9432037577417</v>
       </c>
       <c r="E55">
-        <v>-56.619</v>
+        <v>-54.94200000000001</v>
       </c>
       <c r="F55">
-        <v>88.881</v>
+        <v>90.55799999999999</v>
       </c>
       <c r="G55">
         <v>0.434</v>
@@ -6303,45 +6303,45 @@
         <v>29.9</v>
       </c>
       <c r="M55">
-        <v>4.8262383</v>
+        <v>5.0078574</v>
       </c>
       <c r="N55">
-        <v>25.0737617</v>
+        <v>24.8921426</v>
       </c>
       <c r="O55">
-        <v>5.014752340000001</v>
+        <v>4.978428520000001</v>
       </c>
       <c r="P55">
-        <v>20.05900936</v>
+        <v>19.91371408</v>
       </c>
       <c r="Q55">
-        <v>22.95900936</v>
+        <v>22.81371408</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1105998261906954</v>
+        <v>0.1118604005743292</v>
       </c>
       <c r="T55">
-        <v>1.002432702355778</v>
+        <v>1.021933387159898</v>
       </c>
       <c r="U55">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y55">
-        <v>6.19530121419823</v>
+        <v>5.970617294334301</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6349,22 +6349,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07534538426419143</v>
+        <v>0.07526165021875604</v>
       </c>
       <c r="C56">
-        <v>123.8192037577417</v>
+        <v>122.7502596477217</v>
       </c>
       <c r="D56">
-        <v>213.9432037577417</v>
+        <v>214.5512596477217</v>
       </c>
       <c r="E56">
-        <v>-54.94200000000001</v>
+        <v>-53.265</v>
       </c>
       <c r="F56">
-        <v>90.55799999999999</v>
+        <v>92.235</v>
       </c>
       <c r="G56">
         <v>0.434</v>
@@ -6385,28 +6385,28 @@
         <v>29.9</v>
       </c>
       <c r="M56">
-        <v>5.0078574</v>
+        <v>5.1005955</v>
       </c>
       <c r="N56">
-        <v>24.8921426</v>
+        <v>24.7994045</v>
       </c>
       <c r="O56">
-        <v>4.978428520000001</v>
+        <v>4.959880900000001</v>
       </c>
       <c r="P56">
-        <v>19.91371408</v>
+        <v>19.8395236</v>
       </c>
       <c r="Q56">
-        <v>22.81371408</v>
+        <v>22.7395236</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1118604005743292</v>
+        <v>0.1131770004861245</v>
       </c>
       <c r="T56">
-        <v>1.021933387159898</v>
+        <v>1.042300769066423</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6423,7 +6423,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.970617294334301</v>
+        <v>5.862060616255494</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6431,22 +6431,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07526165021875604</v>
+        <v>0.07517791617332062</v>
       </c>
       <c r="C57">
-        <v>122.7502596477217</v>
+        <v>121.6847817453947</v>
       </c>
       <c r="D57">
-        <v>214.5512596477217</v>
+        <v>215.1627817453947</v>
       </c>
       <c r="E57">
-        <v>-53.265</v>
+        <v>-51.58799999999999</v>
       </c>
       <c r="F57">
-        <v>92.235</v>
+        <v>93.91200000000001</v>
       </c>
       <c r="G57">
         <v>0.434</v>
@@ -6467,28 +6467,28 @@
         <v>29.9</v>
       </c>
       <c r="M57">
-        <v>5.1005955</v>
+        <v>5.193333600000001</v>
       </c>
       <c r="N57">
-        <v>24.7994045</v>
+        <v>24.7066664</v>
       </c>
       <c r="O57">
-        <v>4.959880900000001</v>
+        <v>4.941333280000001</v>
       </c>
       <c r="P57">
-        <v>19.8395236</v>
+        <v>19.76533312</v>
       </c>
       <c r="Q57">
-        <v>22.7395236</v>
+        <v>22.66533312</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1131770004861245</v>
+        <v>0.1145534458484559</v>
       </c>
       <c r="T57">
-        <v>1.042300769066423</v>
+        <v>1.063593941059608</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6505,7 +6505,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.862060616255494</v>
+        <v>5.757380962393789</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6513,22 +6513,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07517791617332062</v>
+        <v>0.07509418212788521</v>
       </c>
       <c r="C58">
-        <v>121.6847817453947</v>
+        <v>120.6227997740266</v>
       </c>
       <c r="D58">
-        <v>215.1627817453947</v>
+        <v>215.7777997740266</v>
       </c>
       <c r="E58">
-        <v>-51.58799999999999</v>
+        <v>-49.911</v>
       </c>
       <c r="F58">
-        <v>93.91200000000001</v>
+        <v>95.589</v>
       </c>
       <c r="G58">
         <v>0.434</v>
@@ -6549,28 +6549,28 @@
         <v>29.9</v>
       </c>
       <c r="M58">
-        <v>5.193333600000001</v>
+        <v>5.2860717</v>
       </c>
       <c r="N58">
-        <v>24.7066664</v>
+        <v>24.6139283</v>
       </c>
       <c r="O58">
-        <v>4.941333280000001</v>
+        <v>4.922785660000001</v>
       </c>
       <c r="P58">
-        <v>19.76533312</v>
+        <v>19.69114264</v>
       </c>
       <c r="Q58">
-        <v>22.66533312</v>
+        <v>22.59114264</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1145534458484559</v>
+        <v>0.1159939119253145</v>
       </c>
       <c r="T58">
-        <v>1.063593941059608</v>
+        <v>1.0858774931455</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.757380962393789</v>
+        <v>5.656374278843021</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6595,22 +6595,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07509418212788521</v>
+        <v>0.0750104480824498</v>
       </c>
       <c r="C59">
-        <v>120.6227997740266</v>
+        <v>119.5643437977003</v>
       </c>
       <c r="D59">
-        <v>215.7777997740266</v>
+        <v>216.3963437977004</v>
       </c>
       <c r="E59">
-        <v>-49.911</v>
+        <v>-48.23399999999999</v>
       </c>
       <c r="F59">
-        <v>95.589</v>
+        <v>97.26600000000001</v>
       </c>
       <c r="G59">
         <v>0.434</v>
@@ -6631,28 +6631,28 @@
         <v>29.9</v>
       </c>
       <c r="M59">
-        <v>5.2860717</v>
+        <v>5.378809800000001</v>
       </c>
       <c r="N59">
-        <v>24.6139283</v>
+        <v>24.5211902</v>
       </c>
       <c r="O59">
-        <v>4.922785660000001</v>
+        <v>4.90423804</v>
       </c>
       <c r="P59">
-        <v>19.69114264</v>
+        <v>19.61695216</v>
       </c>
       <c r="Q59">
-        <v>22.59114264</v>
+        <v>22.51695216</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1159939119253145</v>
+        <v>0.1175029716248805</v>
       </c>
       <c r="T59">
-        <v>1.0858774931455</v>
+        <v>1.109222166759291</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.656374278843021</v>
+        <v>5.558850584380209</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6677,22 +6677,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0750104480824498</v>
+        <v>0.07492671403701441</v>
       </c>
       <c r="C60">
-        <v>119.5643437977004</v>
+        <v>118.5094442262136</v>
       </c>
       <c r="D60">
-        <v>216.3963437977004</v>
+        <v>217.0184442262136</v>
       </c>
       <c r="E60">
-        <v>-48.23400000000001</v>
+        <v>-46.55700000000002</v>
       </c>
       <c r="F60">
-        <v>97.26599999999999</v>
+        <v>98.94299999999998</v>
       </c>
       <c r="G60">
         <v>0.434</v>
@@ -6713,28 +6713,28 @@
         <v>29.9</v>
       </c>
       <c r="M60">
-        <v>5.3788098</v>
+        <v>5.471547899999999</v>
       </c>
       <c r="N60">
-        <v>24.5211902</v>
+        <v>24.4284521</v>
       </c>
       <c r="O60">
-        <v>4.904238040000001</v>
+        <v>4.88569042</v>
       </c>
       <c r="P60">
-        <v>19.61695216</v>
+        <v>19.54276168</v>
       </c>
       <c r="Q60">
-        <v>22.51695216000001</v>
+        <v>22.44276168</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1175029716248805</v>
+        <v>0.1190856439927181</v>
       </c>
       <c r="T60">
-        <v>1.109222166759291</v>
+        <v>1.133705604939609</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.558850584380211</v>
+        <v>5.464632777865292</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6759,22 +6759,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07492671403701441</v>
+        <v>0.074842979991579</v>
       </c>
       <c r="C61">
-        <v>118.5094442262136</v>
+        <v>117.4581318200634</v>
       </c>
       <c r="D61">
-        <v>217.0184442262136</v>
+        <v>217.6441318200634</v>
       </c>
       <c r="E61">
-        <v>-46.55700000000002</v>
+        <v>-44.88000000000001</v>
       </c>
       <c r="F61">
-        <v>98.94299999999998</v>
+        <v>100.62</v>
       </c>
       <c r="G61">
         <v>0.434</v>
@@ -6795,28 +6795,28 @@
         <v>29.9</v>
       </c>
       <c r="M61">
-        <v>5.471547899999999</v>
+        <v>5.564286</v>
       </c>
       <c r="N61">
-        <v>24.4284521</v>
+        <v>24.335714</v>
       </c>
       <c r="O61">
-        <v>4.88569042</v>
+        <v>4.867142800000001</v>
       </c>
       <c r="P61">
-        <v>19.54276168</v>
+        <v>19.4685712</v>
       </c>
       <c r="Q61">
-        <v>22.44276168</v>
+        <v>22.36857120000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1190856439927181</v>
+        <v>0.1207474499789475</v>
       </c>
       <c r="T61">
-        <v>1.133705604939609</v>
+        <v>1.159413215028942</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6833,7 +6833,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.464632777865292</v>
+        <v>5.37355556490087</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6841,22 +6841,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.074842979991579</v>
+        <v>0.07475924594614358</v>
       </c>
       <c r="C62">
-        <v>117.4581318200634</v>
+        <v>116.4104376955156</v>
       </c>
       <c r="D62">
-        <v>217.6441318200634</v>
+        <v>218.2734376955156</v>
       </c>
       <c r="E62">
-        <v>-44.88000000000001</v>
+        <v>-43.203</v>
       </c>
       <c r="F62">
-        <v>100.62</v>
+        <v>102.297</v>
       </c>
       <c r="G62">
         <v>0.434</v>
@@ -6877,28 +6877,28 @@
         <v>29.9</v>
       </c>
       <c r="M62">
-        <v>5.564286</v>
+        <v>5.6570241</v>
       </c>
       <c r="N62">
-        <v>24.335714</v>
+        <v>24.2429759</v>
       </c>
       <c r="O62">
-        <v>4.867142800000001</v>
+        <v>4.84859518</v>
       </c>
       <c r="P62">
-        <v>19.4685712</v>
+        <v>19.39438072</v>
       </c>
       <c r="Q62">
-        <v>22.36857120000001</v>
+        <v>22.29438072</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1207474499789475</v>
+        <v>0.1224944767849835</v>
       </c>
       <c r="T62">
-        <v>1.159413215028942</v>
+        <v>1.186439164097216</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.37355556490087</v>
+        <v>5.285464490066429</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6923,22 +6923,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07475924594614358</v>
+        <v>0.07467551190070817</v>
       </c>
       <c r="C63">
-        <v>116.4104376955156</v>
+        <v>115.3663933297633</v>
       </c>
       <c r="D63">
-        <v>218.2734376955156</v>
+        <v>218.9063933297633</v>
       </c>
       <c r="E63">
-        <v>-43.203</v>
+        <v>-41.52600000000001</v>
       </c>
       <c r="F63">
-        <v>102.297</v>
+        <v>103.974</v>
       </c>
       <c r="G63">
         <v>0.434</v>
@@ -6959,28 +6959,28 @@
         <v>29.9</v>
       </c>
       <c r="M63">
-        <v>5.6570241</v>
+        <v>5.749762199999999</v>
       </c>
       <c r="N63">
-        <v>24.2429759</v>
+        <v>24.1502378</v>
       </c>
       <c r="O63">
-        <v>4.84859518</v>
+        <v>4.830047560000001</v>
       </c>
       <c r="P63">
-        <v>19.39438072</v>
+        <v>19.32019024</v>
       </c>
       <c r="Q63">
-        <v>22.29438072</v>
+        <v>22.22019024</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1224944767849835</v>
+        <v>0.1243334523702847</v>
       </c>
       <c r="T63">
-        <v>1.186439164097216</v>
+        <v>1.214887531537504</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6997,7 +6997,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.285464490066429</v>
+        <v>5.200215062807295</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7005,22 +7005,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07467551190070817</v>
+        <v>0.07459177785527277</v>
       </c>
       <c r="C64">
-        <v>115.3663933297633</v>
+        <v>114.3260305661755</v>
       </c>
       <c r="D64">
-        <v>218.9063933297633</v>
+        <v>219.5430305661755</v>
       </c>
       <c r="E64">
-        <v>-41.52600000000001</v>
+        <v>-39.849</v>
       </c>
       <c r="F64">
-        <v>103.974</v>
+        <v>105.651</v>
       </c>
       <c r="G64">
         <v>0.434</v>
@@ -7041,28 +7041,28 @@
         <v>29.9</v>
       </c>
       <c r="M64">
-        <v>5.749762199999999</v>
+        <v>5.8425003</v>
       </c>
       <c r="N64">
-        <v>24.1502378</v>
+        <v>24.0574997</v>
       </c>
       <c r="O64">
-        <v>4.830047560000001</v>
+        <v>4.811499940000001</v>
       </c>
       <c r="P64">
-        <v>19.32019024</v>
+        <v>19.24599976</v>
       </c>
       <c r="Q64">
-        <v>22.22019024</v>
+        <v>22.14599976</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1243334523702847</v>
+        <v>0.1262718320412778</v>
       </c>
       <c r="T64">
-        <v>1.214887531537504</v>
+        <v>1.244873648569159</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.200215062807295</v>
+        <v>5.117671966572257</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7087,22 +7087,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07459177785527277</v>
+        <v>0.07450804380983736</v>
       </c>
       <c r="C65">
-        <v>114.3260305661755</v>
+        <v>113.2893816196373</v>
       </c>
       <c r="D65">
-        <v>219.5430305661755</v>
+        <v>220.1833816196373</v>
       </c>
       <c r="E65">
-        <v>-39.849</v>
+        <v>-38.17200000000001</v>
       </c>
       <c r="F65">
-        <v>105.651</v>
+        <v>107.328</v>
       </c>
       <c r="G65">
         <v>0.434</v>
@@ -7123,28 +7123,28 @@
         <v>29.9</v>
       </c>
       <c r="M65">
-        <v>5.8425003</v>
+        <v>5.935238399999999</v>
       </c>
       <c r="N65">
-        <v>24.0574997</v>
+        <v>23.9647616</v>
       </c>
       <c r="O65">
-        <v>4.811499940000001</v>
+        <v>4.79295232</v>
       </c>
       <c r="P65">
-        <v>19.24599976</v>
+        <v>19.17180928</v>
       </c>
       <c r="Q65">
-        <v>22.14599976</v>
+        <v>22.07180928</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1262718320412778</v>
+        <v>0.1283178994717705</v>
       </c>
       <c r="T65">
-        <v>1.244873648569159</v>
+        <v>1.276525660991462</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.117671966572257</v>
+        <v>5.037708342094566</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7169,22 +7169,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07450804380983736</v>
+        <v>0.07442430976440197</v>
       </c>
       <c r="C66">
-        <v>113.2893816196373</v>
+        <v>112.2564790819833</v>
       </c>
       <c r="D66">
-        <v>220.1833816196373</v>
+        <v>220.8274790819833</v>
       </c>
       <c r="E66">
-        <v>-38.17200000000001</v>
+        <v>-36.495</v>
       </c>
       <c r="F66">
-        <v>107.328</v>
+        <v>109.005</v>
       </c>
       <c r="G66">
         <v>0.434</v>
@@ -7205,28 +7205,28 @@
         <v>29.9</v>
       </c>
       <c r="M66">
-        <v>5.935238399999999</v>
+        <v>6.0279765</v>
       </c>
       <c r="N66">
-        <v>23.9647616</v>
+        <v>23.8720235</v>
       </c>
       <c r="O66">
-        <v>4.79295232</v>
+        <v>4.774404700000001</v>
       </c>
       <c r="P66">
-        <v>19.17180928</v>
+        <v>19.0976188</v>
       </c>
       <c r="Q66">
-        <v>22.07180928</v>
+        <v>21.9976188</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1283178994717705</v>
+        <v>0.1304808850411485</v>
       </c>
       <c r="T66">
-        <v>1.276525660991462</v>
+        <v>1.309986359837896</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.037708342094566</v>
+        <v>4.960205136831572</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7251,22 +7251,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07442430976440197</v>
+        <v>0.07434057571896656</v>
       </c>
       <c r="C67">
-        <v>112.2564790819833</v>
+        <v>111.2273559275281</v>
       </c>
       <c r="D67">
-        <v>220.8274790819833</v>
+        <v>221.4753559275281</v>
       </c>
       <c r="E67">
-        <v>-36.495</v>
+        <v>-34.818</v>
       </c>
       <c r="F67">
-        <v>109.005</v>
+        <v>110.682</v>
       </c>
       <c r="G67">
         <v>0.434</v>
@@ -7287,28 +7287,28 @@
         <v>29.9</v>
       </c>
       <c r="M67">
-        <v>6.0279765</v>
+        <v>6.1207146</v>
       </c>
       <c r="N67">
-        <v>23.8720235</v>
+        <v>23.7792854</v>
       </c>
       <c r="O67">
-        <v>4.774404700000001</v>
+        <v>4.755857080000001</v>
       </c>
       <c r="P67">
-        <v>19.0976188</v>
+        <v>19.02342832</v>
       </c>
       <c r="Q67">
-        <v>21.9976188</v>
+        <v>21.92342832</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1304808850411485</v>
+        <v>0.132771105055784</v>
       </c>
       <c r="T67">
-        <v>1.309986359837896</v>
+        <v>1.345415335087061</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -7325,7 +7325,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.960205136831572</v>
+        <v>4.885050513546245</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7333,22 +7333,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07434057571896656</v>
+        <v>0.07425684167353114</v>
       </c>
       <c r="C68">
-        <v>111.2273559275281</v>
+        <v>110.2020455186928</v>
       </c>
       <c r="D68">
-        <v>221.4753559275281</v>
+        <v>222.1270455186928</v>
       </c>
       <c r="E68">
-        <v>-34.818</v>
+        <v>-33.14100000000001</v>
       </c>
       <c r="F68">
-        <v>110.682</v>
+        <v>112.359</v>
       </c>
       <c r="G68">
         <v>0.434</v>
@@ -7369,28 +7369,28 @@
         <v>29.9</v>
       </c>
       <c r="M68">
-        <v>6.1207146</v>
+        <v>6.213452699999999</v>
       </c>
       <c r="N68">
-        <v>23.7792854</v>
+        <v>23.6865473</v>
       </c>
       <c r="O68">
-        <v>4.755857080000001</v>
+        <v>4.737309460000001</v>
       </c>
       <c r="P68">
-        <v>19.02342832</v>
+        <v>18.94923784</v>
       </c>
       <c r="Q68">
-        <v>21.92342832</v>
+        <v>21.84923784</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.132771105055784</v>
+        <v>0.1352001262834277</v>
       </c>
       <c r="T68">
-        <v>1.345415335087061</v>
+        <v>1.382991520957389</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.885050513546245</v>
+        <v>4.812139311851526</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7415,22 +7415,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07425684167353114</v>
+        <v>0.07417310762809573</v>
       </c>
       <c r="C69">
-        <v>110.2020455186928</v>
+        <v>109.1805816117317</v>
       </c>
       <c r="D69">
-        <v>222.1270455186928</v>
+        <v>222.7825816117317</v>
       </c>
       <c r="E69">
-        <v>-33.14100000000001</v>
+        <v>-31.464</v>
       </c>
       <c r="F69">
-        <v>112.359</v>
+        <v>114.036</v>
       </c>
       <c r="G69">
         <v>0.434</v>
@@ -7451,28 +7451,28 @@
         <v>29.9</v>
       </c>
       <c r="M69">
-        <v>6.213452699999999</v>
+        <v>6.3061908</v>
       </c>
       <c r="N69">
-        <v>23.6865473</v>
+        <v>23.5938092</v>
       </c>
       <c r="O69">
-        <v>4.737309460000001</v>
+        <v>4.718761840000001</v>
       </c>
       <c r="P69">
-        <v>18.94923784</v>
+        <v>18.87504736</v>
       </c>
       <c r="Q69">
-        <v>21.84923784</v>
+        <v>21.77504736000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1352001262834277</v>
+        <v>0.1377809613377992</v>
       </c>
       <c r="T69">
-        <v>1.382991520957389</v>
+        <v>1.422916218444611</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7489,7 +7489,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.812139311851526</v>
+        <v>4.741372557265473</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7497,22 +7497,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07417310762809573</v>
+        <v>0.07408937358266034</v>
       </c>
       <c r="C70">
-        <v>109.1805816117317</v>
+        <v>108.1629983625616</v>
       </c>
       <c r="D70">
-        <v>222.7825816117317</v>
+        <v>223.4419983625616</v>
       </c>
       <c r="E70">
-        <v>-31.464</v>
+        <v>-29.78699999999999</v>
       </c>
       <c r="F70">
-        <v>114.036</v>
+        <v>115.713</v>
       </c>
       <c r="G70">
         <v>0.434</v>
@@ -7533,28 +7533,28 @@
         <v>29.9</v>
       </c>
       <c r="M70">
-        <v>6.3061908</v>
+        <v>6.3989289</v>
       </c>
       <c r="N70">
-        <v>23.5938092</v>
+        <v>23.5010711</v>
       </c>
       <c r="O70">
-        <v>4.718761840000001</v>
+        <v>4.70021422</v>
       </c>
       <c r="P70">
-        <v>18.87504736</v>
+        <v>18.80085688</v>
       </c>
       <c r="Q70">
-        <v>21.77504736000001</v>
+        <v>21.70085688</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1377809613377992</v>
+        <v>0.1405283018795495</v>
       </c>
       <c r="T70">
-        <v>1.422916218444611</v>
+        <v>1.465416702866493</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7571,7 +7571,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.741372557265473</v>
+        <v>4.672657012957277</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7579,22 +7579,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07408937358266034</v>
+        <v>0.07400563953722492</v>
       </c>
       <c r="C71">
-        <v>108.1629983625616</v>
+        <v>107.149330332694</v>
       </c>
       <c r="D71">
-        <v>223.4419983625616</v>
+        <v>224.105330332694</v>
       </c>
       <c r="E71">
-        <v>-29.78699999999999</v>
+        <v>-28.11</v>
       </c>
       <c r="F71">
-        <v>115.713</v>
+        <v>117.39</v>
       </c>
       <c r="G71">
         <v>0.434</v>
@@ -7615,28 +7615,28 @@
         <v>29.9</v>
       </c>
       <c r="M71">
-        <v>6.3989289</v>
+        <v>6.491667000000001</v>
       </c>
       <c r="N71">
-        <v>23.5010711</v>
+        <v>23.408333</v>
       </c>
       <c r="O71">
-        <v>4.70021422</v>
+        <v>4.681666600000001</v>
       </c>
       <c r="P71">
-        <v>18.80085688</v>
+        <v>18.7266664</v>
       </c>
       <c r="Q71">
-        <v>21.70085688</v>
+        <v>21.6266664</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1405283018795495</v>
+        <v>0.1434587984574164</v>
       </c>
       <c r="T71">
-        <v>1.465416702866493</v>
+        <v>1.510750552916501</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.672657012957277</v>
+        <v>4.605904769915031</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07400563953722492</v>
+        <v>0.07392190549178952</v>
       </c>
       <c r="C72">
-        <v>107.149330332694</v>
+        <v>106.1396124952726</v>
       </c>
       <c r="D72">
-        <v>224.105330332694</v>
+        <v>224.7726124952726</v>
       </c>
       <c r="E72">
-        <v>-28.11</v>
+        <v>-26.43299999999999</v>
       </c>
       <c r="F72">
-        <v>117.39</v>
+        <v>119.067</v>
       </c>
       <c r="G72">
         <v>0.434</v>
@@ -7697,28 +7697,28 @@
         <v>29.9</v>
       </c>
       <c r="M72">
-        <v>6.491667000000001</v>
+        <v>6.584405100000001</v>
       </c>
       <c r="N72">
-        <v>23.408333</v>
+        <v>23.3155949</v>
       </c>
       <c r="O72">
-        <v>4.681666600000001</v>
+        <v>4.66311898</v>
       </c>
       <c r="P72">
-        <v>18.7266664</v>
+        <v>18.65247592</v>
       </c>
       <c r="Q72">
-        <v>21.6266664</v>
+        <v>21.55247592</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1434587984574164</v>
+        <v>0.1465913982475501</v>
       </c>
       <c r="T72">
-        <v>1.510750552916501</v>
+        <v>1.559210875383751</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.605904769915031</v>
+        <v>4.541032871747213</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7743,22 +7743,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07392190549178951</v>
+        <v>0.07527817144635413</v>
       </c>
       <c r="C73">
-        <v>106.1396124952727</v>
+        <v>94.12101303749539</v>
       </c>
       <c r="D73">
-        <v>224.7726124952727</v>
+        <v>214.4310130374954</v>
       </c>
       <c r="E73">
-        <v>-26.43300000000001</v>
+        <v>-24.75600000000001</v>
       </c>
       <c r="F73">
-        <v>119.067</v>
+        <v>120.744</v>
       </c>
       <c r="G73">
         <v>0.434</v>
@@ -7779,45 +7779,45 @@
         <v>29.9</v>
       </c>
       <c r="M73">
-        <v>6.5844051</v>
+        <v>6.979003199999999</v>
       </c>
       <c r="N73">
-        <v>23.3155949</v>
+        <v>22.9209968</v>
       </c>
       <c r="O73">
-        <v>4.66311898</v>
+        <v>4.584199360000001</v>
       </c>
       <c r="P73">
-        <v>18.65247592</v>
+        <v>18.33679744000001</v>
       </c>
       <c r="Q73">
-        <v>21.55247592</v>
+        <v>21.23679744000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.14659139824755</v>
+        <v>0.1499477551655504</v>
       </c>
       <c r="T73">
-        <v>1.55921087538375</v>
+        <v>1.611132649455803</v>
       </c>
       <c r="U73">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V73">
         <v>0.2</v>
       </c>
       <c r="W73">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>4.541032871747214</v>
+        <v>4.284279451254587</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7825,22 +7825,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07527817144635413</v>
+        <v>0.07521443740091871</v>
       </c>
       <c r="C74">
-        <v>94.12101303749539</v>
+        <v>92.90863371819782</v>
       </c>
       <c r="D74">
-        <v>214.4310130374954</v>
+        <v>214.8956337181978</v>
       </c>
       <c r="E74">
-        <v>-24.75600000000001</v>
+        <v>-23.07900000000001</v>
       </c>
       <c r="F74">
-        <v>120.744</v>
+        <v>122.421</v>
       </c>
       <c r="G74">
         <v>0.434</v>
@@ -7861,28 +7861,28 @@
         <v>29.9</v>
       </c>
       <c r="M74">
-        <v>6.979003199999999</v>
+        <v>7.0759338</v>
       </c>
       <c r="N74">
-        <v>22.9209968</v>
+        <v>22.8240662</v>
       </c>
       <c r="O74">
-        <v>4.584199360000001</v>
+        <v>4.56481324</v>
       </c>
       <c r="P74">
-        <v>18.33679744000001</v>
+        <v>18.25925296</v>
       </c>
       <c r="Q74">
-        <v>21.23679744000001</v>
+        <v>21.15925296</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1499477551655504</v>
+        <v>0.1535527311145137</v>
       </c>
       <c r="T74">
-        <v>1.611132649455803</v>
+        <v>1.666900480866526</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.284279451254587</v>
+        <v>4.225590691648359</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7907,22 +7907,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07521443740091871</v>
+        <v>0.07515070335548329</v>
       </c>
       <c r="C75">
-        <v>92.90863371819782</v>
+        <v>91.69827221463811</v>
       </c>
       <c r="D75">
-        <v>214.8956337181978</v>
+        <v>215.3622722146381</v>
       </c>
       <c r="E75">
-        <v>-23.07900000000001</v>
+        <v>-21.40200000000002</v>
       </c>
       <c r="F75">
-        <v>122.421</v>
+        <v>124.098</v>
       </c>
       <c r="G75">
         <v>0.434</v>
@@ -7943,28 +7943,28 @@
         <v>29.9</v>
       </c>
       <c r="M75">
-        <v>7.0759338</v>
+        <v>7.1728644</v>
       </c>
       <c r="N75">
-        <v>22.8240662</v>
+        <v>22.7271356</v>
       </c>
       <c r="O75">
-        <v>4.56481324</v>
+        <v>4.545427120000001</v>
       </c>
       <c r="P75">
-        <v>18.25925296</v>
+        <v>18.18170848</v>
       </c>
       <c r="Q75">
-        <v>21.15925296</v>
+        <v>21.08170848000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1535527311145137</v>
+        <v>0.157435012905705</v>
       </c>
       <c r="T75">
-        <v>1.666900480866526</v>
+        <v>1.72695814546269</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.225590691648359</v>
+        <v>4.168488114734192</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7989,22 +7989,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07515070335548329</v>
+        <v>0.07508696931004789</v>
       </c>
       <c r="C76">
-        <v>91.69827221463811</v>
+        <v>90.48994170027483</v>
       </c>
       <c r="D76">
-        <v>215.3622722146381</v>
+        <v>215.8309417002748</v>
       </c>
       <c r="E76">
-        <v>-21.40200000000002</v>
+        <v>-19.72500000000001</v>
       </c>
       <c r="F76">
-        <v>124.098</v>
+        <v>125.775</v>
       </c>
       <c r="G76">
         <v>0.434</v>
@@ -8025,28 +8025,28 @@
         <v>29.9</v>
       </c>
       <c r="M76">
-        <v>7.1728644</v>
+        <v>7.269795</v>
       </c>
       <c r="N76">
-        <v>22.7271356</v>
+        <v>22.630205</v>
       </c>
       <c r="O76">
-        <v>4.545427120000001</v>
+        <v>4.526041000000001</v>
       </c>
       <c r="P76">
-        <v>18.18170848</v>
+        <v>18.104164</v>
       </c>
       <c r="Q76">
-        <v>21.08170848000001</v>
+        <v>21.00416400000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.157435012905705</v>
+        <v>0.1616278772401916</v>
       </c>
       <c r="T76">
-        <v>1.72695814546269</v>
+        <v>1.791820423226547</v>
       </c>
       <c r="U76">
         <v>0.0578</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.168488114734192</v>
+        <v>4.112908273204403</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8071,22 +8071,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07508696931004789</v>
+        <v>0.07502323526461249</v>
       </c>
       <c r="C77">
-        <v>90.48994170027483</v>
+        <v>89.28365546348871</v>
       </c>
       <c r="D77">
-        <v>215.8309417002748</v>
+        <v>216.3016554634887</v>
       </c>
       <c r="E77">
-        <v>-19.72500000000001</v>
+        <v>-18.048</v>
       </c>
       <c r="F77">
-        <v>125.775</v>
+        <v>127.452</v>
       </c>
       <c r="G77">
         <v>0.434</v>
@@ -8107,28 +8107,28 @@
         <v>29.9</v>
       </c>
       <c r="M77">
-        <v>7.269795</v>
+        <v>7.366725600000001</v>
       </c>
       <c r="N77">
-        <v>22.630205</v>
+        <v>22.5332744</v>
       </c>
       <c r="O77">
-        <v>4.526041000000001</v>
+        <v>4.506654880000001</v>
       </c>
       <c r="P77">
-        <v>18.104164</v>
+        <v>18.02661952</v>
       </c>
       <c r="Q77">
-        <v>21.00416400000001</v>
+        <v>20.92661952000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1616278772401916</v>
+        <v>0.1661701469358854</v>
       </c>
       <c r="T77">
-        <v>1.791820423226547</v>
+        <v>1.862087890804059</v>
       </c>
       <c r="U77">
         <v>0.0578</v>
@@ -8145,7 +8145,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.112908273204403</v>
+        <v>4.058791059083292</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8153,22 +8153,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07502323526461249</v>
+        <v>0.07495950121917708</v>
       </c>
       <c r="C78">
-        <v>89.28365546348871</v>
+        <v>88.07942690883837</v>
       </c>
       <c r="D78">
-        <v>216.3016554634887</v>
+        <v>216.7744269088384</v>
       </c>
       <c r="E78">
-        <v>-18.048</v>
+        <v>-16.37100000000001</v>
       </c>
       <c r="F78">
-        <v>127.452</v>
+        <v>129.129</v>
       </c>
       <c r="G78">
         <v>0.434</v>
@@ -8189,28 +8189,28 @@
         <v>29.9</v>
       </c>
       <c r="M78">
-        <v>7.366725600000001</v>
+        <v>7.4636562</v>
       </c>
       <c r="N78">
-        <v>22.5332744</v>
+        <v>22.4363438</v>
       </c>
       <c r="O78">
-        <v>4.506654880000001</v>
+        <v>4.487268760000001</v>
       </c>
       <c r="P78">
-        <v>18.02661952</v>
+        <v>17.94907504</v>
       </c>
       <c r="Q78">
-        <v>20.92661952000001</v>
+        <v>20.84907504000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1661701469358854</v>
+        <v>0.1711073966051178</v>
       </c>
       <c r="T78">
-        <v>1.862087890804059</v>
+        <v>1.938465572953528</v>
       </c>
       <c r="U78">
         <v>0.0578</v>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>4.058791059083292</v>
+        <v>4.006079486887406</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8235,22 +8235,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07495950121917708</v>
+        <v>0.07707976717374168</v>
       </c>
       <c r="C79">
-        <v>88.07942690883837</v>
+        <v>71.70860151550559</v>
       </c>
       <c r="D79">
-        <v>216.7744269088384</v>
+        <v>202.0806015155056</v>
       </c>
       <c r="E79">
-        <v>-16.37100000000001</v>
+        <v>-14.69400000000002</v>
       </c>
       <c r="F79">
-        <v>129.129</v>
+        <v>130.806</v>
       </c>
       <c r="G79">
         <v>0.434</v>
@@ -8271,45 +8271,45 @@
         <v>29.9</v>
       </c>
       <c r="M79">
-        <v>7.4636562</v>
+        <v>8.018407799999999</v>
       </c>
       <c r="N79">
-        <v>22.4363438</v>
+        <v>21.8815922</v>
       </c>
       <c r="O79">
-        <v>4.487268760000001</v>
+        <v>4.376318440000001</v>
       </c>
       <c r="P79">
-        <v>17.94907504</v>
+        <v>17.50527376</v>
       </c>
       <c r="Q79">
-        <v>20.84907504000001</v>
+        <v>20.40527376</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1711073966051178</v>
+        <v>0.1764934871533713</v>
       </c>
       <c r="T79">
-        <v>1.938465572953528</v>
+        <v>2.021786680752949</v>
       </c>
       <c r="U79">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V79">
         <v>0.2</v>
       </c>
       <c r="W79">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>4.006079486887406</v>
+        <v>3.72891984865125</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8317,22 +8317,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07707976717374168</v>
+        <v>0.07704403312830627</v>
       </c>
       <c r="C80">
-        <v>71.70860151550559</v>
+        <v>70.2627226824342</v>
       </c>
       <c r="D80">
-        <v>202.0806015155056</v>
+        <v>202.3117226824342</v>
       </c>
       <c r="E80">
-        <v>-14.69400000000002</v>
+        <v>-13.017</v>
       </c>
       <c r="F80">
-        <v>130.806</v>
+        <v>132.483</v>
       </c>
       <c r="G80">
         <v>0.434</v>
@@ -8353,28 +8353,28 @@
         <v>29.9</v>
       </c>
       <c r="M80">
-        <v>8.018407799999999</v>
+        <v>8.1212079</v>
       </c>
       <c r="N80">
-        <v>21.8815922</v>
+        <v>21.7787921</v>
       </c>
       <c r="O80">
-        <v>4.376318440000001</v>
+        <v>4.355758420000001</v>
       </c>
       <c r="P80">
-        <v>17.50527376</v>
+        <v>17.42303368</v>
       </c>
       <c r="Q80">
-        <v>20.40527376</v>
+        <v>20.32303368000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1764934871533713</v>
+        <v>0.1823925387062204</v>
       </c>
       <c r="T80">
-        <v>2.021786680752949</v>
+        <v>2.113043132152315</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8391,7 +8391,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.72891984865125</v>
+        <v>3.681718331579715</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8399,22 +8399,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07704403312830627</v>
+        <v>0.07700829908287087</v>
       </c>
       <c r="C81">
-        <v>70.2627226824342</v>
+        <v>68.81737312487746</v>
       </c>
       <c r="D81">
-        <v>202.3117226824342</v>
+        <v>202.5433731248775</v>
       </c>
       <c r="E81">
-        <v>-13.017</v>
+        <v>-11.34</v>
       </c>
       <c r="F81">
-        <v>132.483</v>
+        <v>134.16</v>
       </c>
       <c r="G81">
         <v>0.434</v>
@@ -8435,28 +8435,28 @@
         <v>29.9</v>
       </c>
       <c r="M81">
-        <v>8.1212079</v>
+        <v>8.224008</v>
       </c>
       <c r="N81">
-        <v>21.7787921</v>
+        <v>21.675992</v>
       </c>
       <c r="O81">
-        <v>4.355758420000001</v>
+        <v>4.3351984</v>
       </c>
       <c r="P81">
-        <v>17.42303368</v>
+        <v>17.3407936</v>
       </c>
       <c r="Q81">
-        <v>20.32303368000001</v>
+        <v>20.2407936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1823925387062204</v>
+        <v>0.1888814954143543</v>
       </c>
       <c r="T81">
-        <v>2.113043132152315</v>
+        <v>2.213425228691618</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.681718331579715</v>
+        <v>3.635696852434969</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8481,22 +8481,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07700829908287087</v>
+        <v>0.07697256503743546</v>
       </c>
       <c r="C82">
-        <v>68.81737312487746</v>
+        <v>67.3725546630086</v>
       </c>
       <c r="D82">
-        <v>202.5433731248775</v>
+        <v>202.7755546630086</v>
       </c>
       <c r="E82">
-        <v>-11.34</v>
+        <v>-9.663000000000011</v>
       </c>
       <c r="F82">
-        <v>134.16</v>
+        <v>135.837</v>
       </c>
       <c r="G82">
         <v>0.434</v>
@@ -8517,28 +8517,28 @@
         <v>29.9</v>
       </c>
       <c r="M82">
-        <v>8.224008</v>
+        <v>8.326808099999999</v>
       </c>
       <c r="N82">
-        <v>21.675992</v>
+        <v>21.5731919</v>
       </c>
       <c r="O82">
-        <v>4.3351984</v>
+        <v>4.314638380000001</v>
       </c>
       <c r="P82">
-        <v>17.3407936</v>
+        <v>17.25855352</v>
       </c>
       <c r="Q82">
-        <v>20.2407936</v>
+        <v>20.15855352000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1888814954143543</v>
+        <v>0.1960535001970287</v>
       </c>
       <c r="T82">
-        <v>2.213425228691618</v>
+        <v>2.324373861708741</v>
       </c>
       <c r="U82">
         <v>0.0613</v>
@@ -8555,7 +8555,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.635696852434969</v>
+        <v>3.590811706108612</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8563,22 +8563,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07697256503743546</v>
+        <v>0.07693683099200005</v>
       </c>
       <c r="C83">
-        <v>67.3725546630086</v>
+        <v>65.92826912535642</v>
       </c>
       <c r="D83">
-        <v>202.7755546630086</v>
+        <v>203.0082691253564</v>
       </c>
       <c r="E83">
-        <v>-9.663000000000011</v>
+        <v>-7.98599999999999</v>
       </c>
       <c r="F83">
-        <v>135.837</v>
+        <v>137.514</v>
       </c>
       <c r="G83">
         <v>0.434</v>
@@ -8599,28 +8599,28 @@
         <v>29.9</v>
       </c>
       <c r="M83">
-        <v>8.326808099999999</v>
+        <v>8.429608200000001</v>
       </c>
       <c r="N83">
-        <v>21.5731919</v>
+        <v>21.4703918</v>
       </c>
       <c r="O83">
-        <v>4.314638380000001</v>
+        <v>4.29407836</v>
       </c>
       <c r="P83">
-        <v>17.25855352</v>
+        <v>17.17631344</v>
       </c>
       <c r="Q83">
-        <v>20.15855352000001</v>
+        <v>20.07631344</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1960535001970287</v>
+        <v>0.2040223944000003</v>
       </c>
       <c r="T83">
-        <v>2.324373861708741</v>
+        <v>2.447650120616657</v>
       </c>
       <c r="U83">
         <v>0.0613</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.590811706108612</v>
+        <v>3.54702131944875</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8645,22 +8645,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07693683099200005</v>
+        <v>0.07690109694656463</v>
       </c>
       <c r="C84">
-        <v>65.92826912535642</v>
+        <v>64.48451834885341</v>
       </c>
       <c r="D84">
-        <v>203.0082691253564</v>
+        <v>203.2415183488534</v>
       </c>
       <c r="E84">
-        <v>-7.98599999999999</v>
+        <v>-6.308999999999997</v>
       </c>
       <c r="F84">
-        <v>137.514</v>
+        <v>139.191</v>
       </c>
       <c r="G84">
         <v>0.434</v>
@@ -8681,28 +8681,28 @@
         <v>29.9</v>
       </c>
       <c r="M84">
-        <v>8.429608200000001</v>
+        <v>8.5324083</v>
       </c>
       <c r="N84">
-        <v>21.4703918</v>
+        <v>21.3675917</v>
       </c>
       <c r="O84">
-        <v>4.29407836</v>
+        <v>4.273518340000001</v>
       </c>
       <c r="P84">
-        <v>17.17631344</v>
+        <v>17.09407336</v>
       </c>
       <c r="Q84">
-        <v>20.07631344</v>
+        <v>19.99407336000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2040223944000003</v>
+        <v>0.2129288055680273</v>
       </c>
       <c r="T84">
-        <v>2.447650120616657</v>
+        <v>2.585429468807856</v>
       </c>
       <c r="U84">
         <v>0.0613</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.54702131944875</v>
+        <v>3.504286122828885</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8727,22 +8727,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07690109694656463</v>
+        <v>0.07874696290112923</v>
       </c>
       <c r="C85">
-        <v>64.48451834885341</v>
+        <v>51.42083604979069</v>
       </c>
       <c r="D85">
-        <v>203.2415183488534</v>
+        <v>191.8548360497907</v>
       </c>
       <c r="E85">
-        <v>-6.308999999999997</v>
+        <v>-4.632000000000005</v>
       </c>
       <c r="F85">
-        <v>139.191</v>
+        <v>140.868</v>
       </c>
       <c r="G85">
         <v>0.434</v>
@@ -8763,45 +8763,45 @@
         <v>29.9</v>
       </c>
       <c r="M85">
-        <v>8.5324083</v>
+        <v>9.029638800000001</v>
       </c>
       <c r="N85">
-        <v>21.3675917</v>
+        <v>20.8703612</v>
       </c>
       <c r="O85">
-        <v>4.273518340000001</v>
+        <v>4.17407224</v>
       </c>
       <c r="P85">
-        <v>17.09407336</v>
+        <v>16.69628896</v>
       </c>
       <c r="Q85">
-        <v>19.99407336000001</v>
+        <v>19.59628896</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2129288055680273</v>
+        <v>0.2229485181320578</v>
       </c>
       <c r="T85">
-        <v>2.585429468807856</v>
+        <v>2.740431235522956</v>
       </c>
       <c r="U85">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V85">
         <v>0.2</v>
       </c>
       <c r="W85">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.504286122828885</v>
+        <v>3.311317391787587</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8809,22 +8809,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07874696290112923</v>
+        <v>0.07873362885569382</v>
       </c>
       <c r="C86">
-        <v>51.42083604979069</v>
+        <v>49.82151352384315</v>
       </c>
       <c r="D86">
-        <v>191.8548360497907</v>
+        <v>191.9325135238431</v>
       </c>
       <c r="E86">
-        <v>-4.632000000000005</v>
+        <v>-2.955000000000013</v>
       </c>
       <c r="F86">
-        <v>140.868</v>
+        <v>142.545</v>
       </c>
       <c r="G86">
         <v>0.434</v>
@@ -8845,28 +8845,28 @@
         <v>29.9</v>
       </c>
       <c r="M86">
-        <v>9.029638800000001</v>
+        <v>9.1371345</v>
       </c>
       <c r="N86">
-        <v>20.8703612</v>
+        <v>20.7628655</v>
       </c>
       <c r="O86">
-        <v>4.17407224</v>
+        <v>4.152573100000001</v>
       </c>
       <c r="P86">
-        <v>16.69628896</v>
+        <v>16.6102924</v>
       </c>
       <c r="Q86">
-        <v>19.59628896</v>
+        <v>19.5102924</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2229485181320577</v>
+        <v>0.2343041923712922</v>
       </c>
       <c r="T86">
-        <v>2.740431235522954</v>
+        <v>2.916099904466734</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.311317391787587</v>
+        <v>3.272360716590087</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8891,22 +8891,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07873362885569382</v>
+        <v>0.07872029481025841</v>
       </c>
       <c r="C87">
-        <v>49.82151352384315</v>
+        <v>48.22225392290733</v>
       </c>
       <c r="D87">
-        <v>191.9325135238431</v>
+        <v>192.0102539229073</v>
       </c>
       <c r="E87">
-        <v>-2.955000000000013</v>
+        <v>-1.27800000000002</v>
       </c>
       <c r="F87">
-        <v>142.545</v>
+        <v>144.222</v>
       </c>
       <c r="G87">
         <v>0.434</v>
@@ -8927,28 +8927,28 @@
         <v>29.9</v>
       </c>
       <c r="M87">
-        <v>9.1371345</v>
+        <v>9.2446302</v>
       </c>
       <c r="N87">
-        <v>20.7628655</v>
+        <v>20.6553698</v>
       </c>
       <c r="O87">
-        <v>4.152573100000001</v>
+        <v>4.131073960000001</v>
       </c>
       <c r="P87">
-        <v>16.6102924</v>
+        <v>16.52429584</v>
       </c>
       <c r="Q87">
-        <v>19.5102924</v>
+        <v>19.42429584</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2343041923712922</v>
+        <v>0.2472821057875601</v>
       </c>
       <c r="T87">
-        <v>2.916099904466734</v>
+        <v>3.116864097545338</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.272360716590087</v>
+        <v>3.234310010583225</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8973,22 +8973,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07872029481025841</v>
+        <v>0.078706960764823</v>
       </c>
       <c r="C88">
-        <v>48.22225392290733</v>
+        <v>46.62305732347562</v>
       </c>
       <c r="D88">
-        <v>192.0102539229073</v>
+        <v>192.0880573234756</v>
       </c>
       <c r="E88">
-        <v>-1.27800000000002</v>
+        <v>0.3990000000000009</v>
       </c>
       <c r="F88">
-        <v>144.222</v>
+        <v>145.899</v>
       </c>
       <c r="G88">
         <v>0.434</v>
@@ -9009,28 +9009,28 @@
         <v>29.9</v>
       </c>
       <c r="M88">
-        <v>9.2446302</v>
+        <v>9.352125900000001</v>
       </c>
       <c r="N88">
-        <v>20.6553698</v>
+        <v>20.5478741</v>
       </c>
       <c r="O88">
-        <v>4.131073960000001</v>
+        <v>4.109574820000001</v>
       </c>
       <c r="P88">
-        <v>16.52429584</v>
+        <v>16.43829928</v>
       </c>
       <c r="Q88">
-        <v>19.42429584</v>
+        <v>19.33829928</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2472821057875601</v>
+        <v>0.2622566212678692</v>
       </c>
       <c r="T88">
-        <v>3.116864097545338</v>
+        <v>3.348515089559112</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.234310010583225</v>
+        <v>3.197134033450084</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9055,22 +9055,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.078706960764823</v>
+        <v>0.07869362671938761</v>
       </c>
       <c r="C89">
-        <v>46.62305732347562</v>
+        <v>45.0239238021646</v>
       </c>
       <c r="D89">
-        <v>192.0880573234756</v>
+        <v>192.1659238021646</v>
       </c>
       <c r="E89">
-        <v>0.3990000000000009</v>
+        <v>2.075999999999993</v>
       </c>
       <c r="F89">
-        <v>145.899</v>
+        <v>147.576</v>
       </c>
       <c r="G89">
         <v>0.434</v>
@@ -9091,28 +9091,28 @@
         <v>29.9</v>
       </c>
       <c r="M89">
-        <v>9.352125900000001</v>
+        <v>9.4596216</v>
       </c>
       <c r="N89">
-        <v>20.5478741</v>
+        <v>20.4403784</v>
       </c>
       <c r="O89">
-        <v>4.109574820000001</v>
+        <v>4.08807568</v>
       </c>
       <c r="P89">
-        <v>16.43829928</v>
+        <v>16.35230272</v>
       </c>
       <c r="Q89">
-        <v>19.33829928</v>
+        <v>19.25230272</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2622566212678692</v>
+        <v>0.27972688932823</v>
       </c>
       <c r="T89">
-        <v>3.348515089559112</v>
+        <v>3.61877458024185</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -9129,7 +9129,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.197134033450084</v>
+        <v>3.160802964888151</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9137,22 +9137,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07869362671938761</v>
+        <v>0.07868029267395221</v>
       </c>
       <c r="C90">
-        <v>45.0239238021646</v>
+        <v>43.42485343571505</v>
       </c>
       <c r="D90">
-        <v>192.1659238021646</v>
+        <v>192.243853435715</v>
       </c>
       <c r="E90">
-        <v>2.075999999999993</v>
+        <v>3.752999999999986</v>
       </c>
       <c r="F90">
-        <v>147.576</v>
+        <v>149.253</v>
       </c>
       <c r="G90">
         <v>0.434</v>
@@ -9173,28 +9173,28 @@
         <v>29.9</v>
       </c>
       <c r="M90">
-        <v>9.4596216</v>
+        <v>9.5671173</v>
       </c>
       <c r="N90">
-        <v>20.4403784</v>
+        <v>20.3328827</v>
       </c>
       <c r="O90">
-        <v>4.08807568</v>
+        <v>4.066576540000001</v>
       </c>
       <c r="P90">
-        <v>16.35230272</v>
+        <v>16.26630616</v>
       </c>
       <c r="Q90">
-        <v>19.25230272</v>
+        <v>19.16630616</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.27972688932823</v>
+        <v>0.3003735697632018</v>
       </c>
       <c r="T90">
-        <v>3.61877458024185</v>
+        <v>3.938172160139631</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -9211,7 +9211,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.160802964888151</v>
+        <v>3.125288324833229</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9219,22 +9219,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07868029267395221</v>
+        <v>0.0786669586285168</v>
       </c>
       <c r="C91">
-        <v>43.42485343571505</v>
+        <v>41.82584630099242</v>
       </c>
       <c r="D91">
-        <v>192.243853435715</v>
+        <v>192.3218463009924</v>
       </c>
       <c r="E91">
-        <v>3.752999999999986</v>
+        <v>5.430000000000007</v>
       </c>
       <c r="F91">
-        <v>149.253</v>
+        <v>150.93</v>
       </c>
       <c r="G91">
         <v>0.434</v>
@@ -9255,28 +9255,28 @@
         <v>29.9</v>
       </c>
       <c r="M91">
-        <v>9.5671173</v>
+        <v>9.674613000000001</v>
       </c>
       <c r="N91">
-        <v>20.3328827</v>
+        <v>20.225387</v>
       </c>
       <c r="O91">
-        <v>4.066576540000001</v>
+        <v>4.0450774</v>
       </c>
       <c r="P91">
-        <v>16.26630616</v>
+        <v>16.1803096</v>
       </c>
       <c r="Q91">
-        <v>19.16630616</v>
+        <v>19.0803096</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3003735697632018</v>
+        <v>0.325149586285168</v>
       </c>
       <c r="T91">
-        <v>3.938172160139631</v>
+        <v>4.321449256016968</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.125288324833229</v>
+        <v>3.090562899001748</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9301,22 +9301,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0786669586285168</v>
+        <v>0.07865362458308139</v>
       </c>
       <c r="C92">
-        <v>41.82584630099242</v>
+        <v>40.22690247498664</v>
       </c>
       <c r="D92">
-        <v>192.3218463009924</v>
+        <v>192.3999024749866</v>
       </c>
       <c r="E92">
-        <v>5.430000000000007</v>
+        <v>7.106999999999999</v>
       </c>
       <c r="F92">
-        <v>150.93</v>
+        <v>152.607</v>
       </c>
       <c r="G92">
         <v>0.434</v>
@@ -9337,28 +9337,28 @@
         <v>29.9</v>
       </c>
       <c r="M92">
-        <v>9.674613000000001</v>
+        <v>9.7821087</v>
       </c>
       <c r="N92">
-        <v>20.225387</v>
+        <v>20.1178913</v>
       </c>
       <c r="O92">
-        <v>4.0450774</v>
+        <v>4.023578260000001</v>
       </c>
       <c r="P92">
-        <v>16.1803096</v>
+        <v>16.09431304</v>
       </c>
       <c r="Q92">
-        <v>19.0803096</v>
+        <v>18.99431304000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.325149586285168</v>
+        <v>0.3554313842564599</v>
       </c>
       <c r="T92">
-        <v>4.321449256016968</v>
+        <v>4.789899039867046</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.090562899001748</v>
+        <v>3.056600669342389</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9383,22 +9383,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07865362458308139</v>
+        <v>0.07864029053764598</v>
       </c>
       <c r="C93">
-        <v>40.22690247498664</v>
+        <v>38.628022034813</v>
       </c>
       <c r="D93">
-        <v>192.3999024749866</v>
+        <v>192.478022034813</v>
       </c>
       <c r="E93">
-        <v>7.106999999999999</v>
+        <v>8.783999999999992</v>
       </c>
       <c r="F93">
-        <v>152.607</v>
+        <v>154.284</v>
       </c>
       <c r="G93">
         <v>0.434</v>
@@ -9419,28 +9419,28 @@
         <v>29.9</v>
       </c>
       <c r="M93">
-        <v>9.7821087</v>
+        <v>9.8896044</v>
       </c>
       <c r="N93">
-        <v>20.1178913</v>
+        <v>20.0103956</v>
       </c>
       <c r="O93">
-        <v>4.023578260000001</v>
+        <v>4.00207912</v>
       </c>
       <c r="P93">
-        <v>16.09431304</v>
+        <v>16.00831648</v>
       </c>
       <c r="Q93">
-        <v>18.99431304000001</v>
+        <v>18.90831648</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3554313842564599</v>
+        <v>0.3932836317205749</v>
       </c>
       <c r="T93">
-        <v>4.789899039867046</v>
+        <v>5.375461269679644</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -9457,7 +9457,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.056600669342389</v>
+        <v>3.02337674902345</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9465,22 +9465,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07864029053764598</v>
+        <v>0.08443015649221058</v>
       </c>
       <c r="C94">
-        <v>38.628022034813</v>
+        <v>8.102525213268649</v>
       </c>
       <c r="D94">
-        <v>192.478022034813</v>
+        <v>163.6295252132686</v>
       </c>
       <c r="E94">
-        <v>8.783999999999992</v>
+        <v>10.46099999999998</v>
       </c>
       <c r="F94">
-        <v>154.284</v>
+        <v>155.961</v>
       </c>
       <c r="G94">
         <v>0.434</v>
@@ -9501,45 +9501,45 @@
         <v>29.9</v>
       </c>
       <c r="M94">
-        <v>9.8896044</v>
+        <v>11.2135959</v>
       </c>
       <c r="N94">
-        <v>20.0103956</v>
+        <v>18.6864041</v>
       </c>
       <c r="O94">
-        <v>4.00207912</v>
+        <v>3.737280820000001</v>
       </c>
       <c r="P94">
-        <v>16.00831648</v>
+        <v>14.94912328</v>
       </c>
       <c r="Q94">
-        <v>18.90831648</v>
+        <v>17.84912328000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3932836317205749</v>
+        <v>0.4419508070315799</v>
       </c>
       <c r="T94">
-        <v>5.375461269679644</v>
+        <v>6.128326993724413</v>
       </c>
       <c r="U94">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V94">
         <v>0.2</v>
       </c>
       <c r="W94">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>3.02337674902345</v>
+        <v>2.666406054457518</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9547,22 +9547,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08443015649221058</v>
+        <v>0.08447922244677517</v>
       </c>
       <c r="C95">
-        <v>8.102525213268649</v>
+        <v>6.217955403389794</v>
       </c>
       <c r="D95">
-        <v>163.6295252132686</v>
+        <v>163.4219554033898</v>
       </c>
       <c r="E95">
-        <v>10.46099999999998</v>
+        <v>12.13800000000001</v>
       </c>
       <c r="F95">
-        <v>155.961</v>
+        <v>157.638</v>
       </c>
       <c r="G95">
         <v>0.434</v>
@@ -9583,28 +9583,28 @@
         <v>29.9</v>
       </c>
       <c r="M95">
-        <v>11.2135959</v>
+        <v>11.3341722</v>
       </c>
       <c r="N95">
-        <v>18.6864041</v>
+        <v>18.5658278</v>
       </c>
       <c r="O95">
-        <v>3.737280820000001</v>
+        <v>3.71316556</v>
       </c>
       <c r="P95">
-        <v>14.94912328</v>
+        <v>14.85266224</v>
       </c>
       <c r="Q95">
-        <v>17.84912328000001</v>
+        <v>17.75266224</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4419508070315799</v>
+        <v>0.5068403741129197</v>
       </c>
       <c r="T95">
-        <v>6.128326993724413</v>
+        <v>7.132147959117439</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9621,7 +9621,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.666406054457518</v>
+        <v>2.638040032601587</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9629,22 +9629,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08447922244677517</v>
+        <v>0.08452828840133976</v>
       </c>
       <c r="C96">
-        <v>6.217955403389794</v>
+        <v>4.33391154553621</v>
       </c>
       <c r="D96">
-        <v>163.4219554033898</v>
+        <v>163.2149115455362</v>
       </c>
       <c r="E96">
-        <v>12.13800000000001</v>
+        <v>13.815</v>
       </c>
       <c r="F96">
-        <v>157.638</v>
+        <v>159.315</v>
       </c>
       <c r="G96">
         <v>0.434</v>
@@ -9665,28 +9665,28 @@
         <v>29.9</v>
       </c>
       <c r="M96">
-        <v>11.3341722</v>
+        <v>11.4547485</v>
       </c>
       <c r="N96">
-        <v>18.5658278</v>
+        <v>18.4452515</v>
       </c>
       <c r="O96">
-        <v>3.71316556</v>
+        <v>3.6890503</v>
       </c>
       <c r="P96">
-        <v>14.85266224</v>
+        <v>14.7562012</v>
       </c>
       <c r="Q96">
-        <v>17.75266224</v>
+        <v>17.65620120000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5068403741129197</v>
+        <v>0.5976857680267958</v>
       </c>
       <c r="T96">
-        <v>7.132147959117439</v>
+        <v>8.537497310667678</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.638040032601587</v>
+        <v>2.610271190153149</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9711,22 +9711,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08452828840133976</v>
+        <v>0.08457735435590436</v>
       </c>
       <c r="C97">
-        <v>4.33391154553621</v>
+        <v>2.450391643207212</v>
       </c>
       <c r="D97">
-        <v>163.2149115455362</v>
+        <v>163.0083916432072</v>
       </c>
       <c r="E97">
-        <v>13.815</v>
+        <v>15.49199999999999</v>
       </c>
       <c r="F97">
-        <v>159.315</v>
+        <v>160.992</v>
       </c>
       <c r="G97">
         <v>0.434</v>
@@ -9747,28 +9747,28 @@
         <v>29.9</v>
       </c>
       <c r="M97">
-        <v>11.4547485</v>
+        <v>11.5753248</v>
       </c>
       <c r="N97">
-        <v>18.4452515</v>
+        <v>18.3246752</v>
       </c>
       <c r="O97">
-        <v>3.6890503</v>
+        <v>3.66493504</v>
       </c>
       <c r="P97">
-        <v>14.7562012</v>
+        <v>14.65974016</v>
       </c>
       <c r="Q97">
-        <v>17.65620120000001</v>
+        <v>17.55974016</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5976857680267958</v>
+        <v>0.7339538588976099</v>
       </c>
       <c r="T97">
-        <v>8.537497310667678</v>
+        <v>10.64552133799303</v>
       </c>
       <c r="U97">
         <v>0.07190000000000001</v>
@@ -9785,7 +9785,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.610271190153149</v>
+        <v>2.58308086525572</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9793,22 +9793,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08457735435590436</v>
+        <v>0.08462642031046895</v>
       </c>
       <c r="C98">
-        <v>2.450391643207212</v>
+        <v>0.5673937099943203</v>
       </c>
       <c r="D98">
-        <v>163.0083916432072</v>
+        <v>162.8023937099943</v>
       </c>
       <c r="E98">
-        <v>15.49199999999999</v>
+        <v>17.16899999999998</v>
       </c>
       <c r="F98">
-        <v>160.992</v>
+        <v>162.669</v>
       </c>
       <c r="G98">
         <v>0.434</v>
@@ -9829,28 +9829,28 @@
         <v>29.9</v>
       </c>
       <c r="M98">
-        <v>11.5753248</v>
+        <v>11.6959011</v>
       </c>
       <c r="N98">
-        <v>18.3246752</v>
+        <v>18.2040989</v>
       </c>
       <c r="O98">
-        <v>3.66493504</v>
+        <v>3.640819780000001</v>
       </c>
       <c r="P98">
-        <v>14.65974016</v>
+        <v>14.56327912</v>
       </c>
       <c r="Q98">
-        <v>17.55974016</v>
+        <v>17.46327912</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7339538588976081</v>
+        <v>0.9610673436822973</v>
       </c>
       <c r="T98">
-        <v>10.64552133799301</v>
+        <v>14.15889471686859</v>
       </c>
       <c r="U98">
         <v>0.07190000000000001</v>
@@ -9867,7 +9867,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.58308086525572</v>
+        <v>2.556451165613909</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9875,22 +9875,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08462642031046895</v>
+        <v>0.08467548626503354</v>
       </c>
       <c r="C99">
-        <v>0.5673937099943203</v>
+        <v>-1.315084230482711</v>
       </c>
       <c r="D99">
-        <v>162.8023937099943</v>
+        <v>162.5969157695173</v>
       </c>
       <c r="E99">
-        <v>17.16899999999998</v>
+        <v>18.84599999999998</v>
       </c>
       <c r="F99">
-        <v>162.669</v>
+        <v>164.346</v>
       </c>
       <c r="G99">
         <v>0.434</v>
@@ -9911,28 +9911,28 @@
         <v>29.9</v>
       </c>
       <c r="M99">
-        <v>11.6959011</v>
+        <v>11.8164774</v>
       </c>
       <c r="N99">
-        <v>18.2040989</v>
+        <v>18.0835226</v>
       </c>
       <c r="O99">
-        <v>3.640819780000001</v>
+        <v>3.616704520000001</v>
       </c>
       <c r="P99">
-        <v>14.56327912</v>
+        <v>14.46681808</v>
       </c>
       <c r="Q99">
-        <v>17.46327912</v>
+        <v>17.36681808</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9610673436822973</v>
+        <v>1.415294313251676</v>
       </c>
       <c r="T99">
-        <v>14.15889471686859</v>
+        <v>21.18564147461974</v>
       </c>
       <c r="U99">
         <v>0.07190000000000001</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.556451165613909</v>
+        <v>2.530364929230094</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9957,22 +9957,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08467548626503354</v>
+        <v>0.08472455221959814</v>
       </c>
       <c r="C100">
-        <v>-1.315084230482711</v>
+        <v>-3.197044144638767</v>
       </c>
       <c r="D100">
-        <v>162.5969157695173</v>
+        <v>162.3919558553612</v>
       </c>
       <c r="E100">
-        <v>18.84599999999998</v>
+        <v>20.523</v>
       </c>
       <c r="F100">
-        <v>164.346</v>
+        <v>166.023</v>
       </c>
       <c r="G100">
         <v>0.434</v>
@@ -9993,28 +9993,28 @@
         <v>29.9</v>
       </c>
       <c r="M100">
-        <v>11.8164774</v>
+        <v>11.9370537</v>
       </c>
       <c r="N100">
-        <v>18.0835226</v>
+        <v>17.9629463</v>
       </c>
       <c r="O100">
-        <v>3.616704520000001</v>
+        <v>3.59258926</v>
       </c>
       <c r="P100">
-        <v>14.46681808</v>
+        <v>14.37035704</v>
       </c>
       <c r="Q100">
-        <v>17.36681808</v>
+        <v>17.27035704</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.415294313251676</v>
+        <v>2.77797522195981</v>
       </c>
       <c r="T100">
-        <v>21.18564147461974</v>
+        <v>42.26588174787322</v>
       </c>
       <c r="U100">
         <v>0.07190000000000001</v>
@@ -10031,91 +10031,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.530364929230094</v>
+        <v>2.504805687520699</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08472455221959814</v>
-      </c>
-      <c r="C101">
-        <v>-3.197044144638767</v>
-      </c>
-      <c r="D101">
-        <v>162.3919558553612</v>
-      </c>
-      <c r="E101">
-        <v>20.523</v>
-      </c>
-      <c r="F101">
-        <v>166.023</v>
-      </c>
-      <c r="G101">
-        <v>0.434</v>
-      </c>
-      <c r="H101">
-        <v>22.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>32.8</v>
-      </c>
-      <c r="K101">
-        <v>2.900000000000002</v>
-      </c>
-      <c r="L101">
-        <v>29.9</v>
-      </c>
-      <c r="M101">
-        <v>11.9370537</v>
-      </c>
-      <c r="N101">
-        <v>17.9629463</v>
-      </c>
-      <c r="O101">
-        <v>3.59258926</v>
-      </c>
-      <c r="P101">
-        <v>14.37035704</v>
-      </c>
-      <c r="Q101">
-        <v>17.27035704</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.77797522195981</v>
-      </c>
-      <c r="T101">
-        <v>42.26588174787322</v>
-      </c>
-      <c r="U101">
-        <v>0.07190000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.05752000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B1/B+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.504805687520699</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
